--- a/research/traditional_assets/database/data/mauritius/mauritius_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_oilfield_svcs_equip.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1038665722069067</v>
+        <v>0.1037490223485963</v>
       </c>
       <c r="C2">
-        <v>224.0934962915892</v>
+        <v>222.304233825402</v>
       </c>
       <c r="D2">
-        <v>219.9834962915892</v>
+        <v>220.4297338254019</v>
       </c>
       <c r="E2">
-        <v>-2.45</v>
+        <v>-0.2145000000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.2355</v>
       </c>
       <c r="G2">
         <v>4.11</v>
@@ -1451,28 +1451,28 @@
         <v>14.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.11244565</v>
       </c>
       <c r="N2">
-        <v>14.1</v>
+        <v>13.98755435</v>
       </c>
       <c r="O2">
-        <v>2.115</v>
+        <v>2.0981331525</v>
       </c>
       <c r="P2">
-        <v>11.985</v>
+        <v>11.8894211975</v>
       </c>
       <c r="Q2">
-        <v>15.685</v>
+        <v>15.5894211975</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1038665722069067</v>
+        <v>0.1043651235844407</v>
       </c>
       <c r="T2">
-        <v>0.7993082229751833</v>
+        <v>0.8061709703441621</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>125.3939125257402</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1037490223485963</v>
+        <v>0.103631472490286</v>
       </c>
       <c r="C3">
-        <v>222.304233825402</v>
+        <v>220.5167854288418</v>
       </c>
       <c r="D3">
-        <v>220.4297338254019</v>
+        <v>220.8777854288418</v>
       </c>
       <c r="E3">
-        <v>-0.2145000000000001</v>
+        <v>2.021</v>
       </c>
       <c r="F3">
-        <v>2.2355</v>
+        <v>4.471</v>
       </c>
       <c r="G3">
         <v>4.11</v>
@@ -1533,28 +1533,28 @@
         <v>14.1</v>
       </c>
       <c r="M3">
-        <v>0.11244565</v>
+        <v>0.2248913</v>
       </c>
       <c r="N3">
-        <v>13.98755435</v>
+        <v>13.8751087</v>
       </c>
       <c r="O3">
-        <v>2.0981331525</v>
+        <v>2.081266305</v>
       </c>
       <c r="P3">
-        <v>11.8894211975</v>
+        <v>11.793842395</v>
       </c>
       <c r="Q3">
-        <v>15.5894211975</v>
+        <v>15.493842395</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1043651235844407</v>
+        <v>0.1048738494798836</v>
       </c>
       <c r="T3">
-        <v>0.8061709703441621</v>
+        <v>0.8131737737818958</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>125.3939125257402</v>
+        <v>62.69695626287011</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.103631472490286</v>
+        <v>0.1035139226319756</v>
       </c>
       <c r="C4">
-        <v>220.5167854288418</v>
+        <v>218.7311621864249</v>
       </c>
       <c r="D4">
-        <v>220.8777854288418</v>
+        <v>221.3276621864249</v>
       </c>
       <c r="E4">
-        <v>2.021</v>
+        <v>4.256499999999999</v>
       </c>
       <c r="F4">
-        <v>4.471</v>
+        <v>6.706499999999999</v>
       </c>
       <c r="G4">
         <v>4.11</v>
@@ -1615,28 +1615,28 @@
         <v>14.1</v>
       </c>
       <c r="M4">
-        <v>0.2248913</v>
+        <v>0.33733695</v>
       </c>
       <c r="N4">
-        <v>13.8751087</v>
+        <v>13.76266305</v>
       </c>
       <c r="O4">
-        <v>2.081266305</v>
+        <v>2.0643994575</v>
       </c>
       <c r="P4">
-        <v>11.793842395</v>
+        <v>11.6982635925</v>
       </c>
       <c r="Q4">
-        <v>15.493842395</v>
+        <v>15.3982635925</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1048738494798836</v>
+        <v>0.105393064569047</v>
       </c>
       <c r="T4">
-        <v>0.8131737737818958</v>
+        <v>0.8203209649193762</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>62.69695626287011</v>
+        <v>41.79797084191341</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1035139226319756</v>
+        <v>0.1033963727736652</v>
       </c>
       <c r="C5">
-        <v>218.7311621864249</v>
+        <v>216.9473752731572</v>
       </c>
       <c r="D5">
-        <v>221.3276621864249</v>
+        <v>221.7793752731572</v>
       </c>
       <c r="E5">
-        <v>4.256499999999999</v>
+        <v>6.492</v>
       </c>
       <c r="F5">
-        <v>6.706499999999999</v>
+        <v>8.942</v>
       </c>
       <c r="G5">
         <v>4.11</v>
@@ -1697,28 +1697,28 @@
         <v>14.1</v>
       </c>
       <c r="M5">
-        <v>0.33733695</v>
+        <v>0.4497826</v>
       </c>
       <c r="N5">
-        <v>13.76266305</v>
+        <v>13.6502174</v>
       </c>
       <c r="O5">
-        <v>2.0643994575</v>
+        <v>2.04753261</v>
       </c>
       <c r="P5">
-        <v>11.6982635925</v>
+        <v>11.60268479</v>
       </c>
       <c r="Q5">
-        <v>15.3982635925</v>
+        <v>15.30268479</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.105393064569047</v>
+        <v>0.1059230966392346</v>
       </c>
       <c r="T5">
-        <v>0.8203209649193762</v>
+        <v>0.8276170558722211</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>41.79797084191341</v>
+        <v>31.34847813143505</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1033963727736652</v>
+        <v>0.1032788229153549</v>
       </c>
       <c r="C6">
-        <v>216.9473752731572</v>
+        <v>215.1654359554611</v>
       </c>
       <c r="D6">
-        <v>221.7793752731572</v>
+        <v>222.2329359554611</v>
       </c>
       <c r="E6">
-        <v>6.492</v>
+        <v>8.727499999999999</v>
       </c>
       <c r="F6">
-        <v>8.942</v>
+        <v>11.1775</v>
       </c>
       <c r="G6">
         <v>4.11</v>
@@ -1779,28 +1779,28 @@
         <v>14.1</v>
       </c>
       <c r="M6">
-        <v>0.4497826</v>
+        <v>0.56222825</v>
       </c>
       <c r="N6">
-        <v>13.6502174</v>
+        <v>13.53777175</v>
       </c>
       <c r="O6">
-        <v>2.04753261</v>
+        <v>2.0306657625</v>
       </c>
       <c r="P6">
-        <v>11.60268479</v>
+        <v>11.5071059875</v>
       </c>
       <c r="Q6">
-        <v>15.30268479</v>
+        <v>15.2071059875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1059230966392346</v>
+        <v>0.1064642872793209</v>
       </c>
       <c r="T6">
-        <v>0.8276170558722211</v>
+        <v>0.8350667487398626</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>31.34847813143505</v>
+        <v>25.07878250514804</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1032788229153549</v>
+        <v>0.1031612730570445</v>
       </c>
       <c r="C7">
-        <v>215.1654359554611</v>
+        <v>213.3853555921119</v>
       </c>
       <c r="D7">
-        <v>222.2329359554611</v>
+        <v>222.6883555921119</v>
       </c>
       <c r="E7">
-        <v>8.727499999999999</v>
+        <v>10.963</v>
       </c>
       <c r="F7">
-        <v>11.1775</v>
+        <v>13.413</v>
       </c>
       <c r="G7">
         <v>4.11</v>
@@ -1861,28 +1861,28 @@
         <v>14.1</v>
       </c>
       <c r="M7">
-        <v>0.56222825</v>
+        <v>0.6746738999999999</v>
       </c>
       <c r="N7">
-        <v>13.53777175</v>
+        <v>13.4253261</v>
       </c>
       <c r="O7">
-        <v>2.0306657625</v>
+        <v>2.013798915</v>
       </c>
       <c r="P7">
-        <v>11.5071059875</v>
+        <v>11.411527185</v>
       </c>
       <c r="Q7">
-        <v>15.2071059875</v>
+        <v>15.111527185</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1064642872793209</v>
+        <v>0.1070169926138771</v>
       </c>
       <c r="T7">
-        <v>0.8350667487398626</v>
+        <v>0.8426749457110709</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.07878250514804</v>
+        <v>20.8989854209567</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1031612730570445</v>
+        <v>0.1030437231987342</v>
       </c>
       <c r="C8">
-        <v>213.3853555921119</v>
+        <v>211.607145635185</v>
       </c>
       <c r="D8">
-        <v>222.6883555921119</v>
+        <v>223.145645635185</v>
       </c>
       <c r="E8">
-        <v>10.963</v>
+        <v>13.1985</v>
       </c>
       <c r="F8">
-        <v>13.413</v>
+        <v>15.6485</v>
       </c>
       <c r="G8">
         <v>4.11</v>
@@ -1943,28 +1943,28 @@
         <v>14.1</v>
       </c>
       <c r="M8">
-        <v>0.6746738999999999</v>
+        <v>0.7871195499999998</v>
       </c>
       <c r="N8">
-        <v>13.4253261</v>
+        <v>13.31288045</v>
       </c>
       <c r="O8">
-        <v>2.013798915</v>
+        <v>1.9969320675</v>
       </c>
       <c r="P8">
-        <v>11.411527185</v>
+        <v>11.3159483825</v>
       </c>
       <c r="Q8">
-        <v>15.111527185</v>
+        <v>15.0159483825</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1070169926138771</v>
+        <v>0.1075815840846604</v>
       </c>
       <c r="T8">
-        <v>0.8426749457110709</v>
+        <v>0.850446759821445</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.8989854209567</v>
+        <v>17.91341607510575</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1030437231987341</v>
+        <v>0.1029261733404238</v>
       </c>
       <c r="C9">
-        <v>211.607145635185</v>
+        <v>209.8308176310174</v>
       </c>
       <c r="D9">
-        <v>223.145645635185</v>
+        <v>223.6048176310174</v>
       </c>
       <c r="E9">
-        <v>13.1985</v>
+        <v>15.434</v>
       </c>
       <c r="F9">
-        <v>15.6485</v>
+        <v>17.884</v>
       </c>
       <c r="G9">
         <v>4.11</v>
@@ -2025,28 +2025,28 @@
         <v>14.1</v>
       </c>
       <c r="M9">
-        <v>0.78711955</v>
+        <v>0.8995652</v>
       </c>
       <c r="N9">
-        <v>13.31288045</v>
+        <v>13.2004348</v>
       </c>
       <c r="O9">
-        <v>1.9969320675</v>
+        <v>1.98006522</v>
       </c>
       <c r="P9">
-        <v>11.3159483825</v>
+        <v>11.22036958</v>
       </c>
       <c r="Q9">
-        <v>15.0159483825</v>
+        <v>14.92036958</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1075815840846604</v>
+        <v>0.1081584492830693</v>
       </c>
       <c r="T9">
-        <v>0.850446759821445</v>
+        <v>0.8583875264124795</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.91341607510574</v>
+        <v>15.67423906571753</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1029261733404238</v>
+        <v>0.1028086234821134</v>
       </c>
       <c r="C10">
-        <v>209.8308176310174</v>
+        <v>208.0563832211784</v>
       </c>
       <c r="D10">
-        <v>223.6048176310174</v>
+        <v>224.0658832211783</v>
       </c>
       <c r="E10">
-        <v>15.434</v>
+        <v>17.6695</v>
       </c>
       <c r="F10">
-        <v>17.884</v>
+        <v>20.1195</v>
       </c>
       <c r="G10">
         <v>4.11</v>
@@ -2107,28 +2107,28 @@
         <v>14.1</v>
       </c>
       <c r="M10">
-        <v>0.8995652</v>
+        <v>1.01201085</v>
       </c>
       <c r="N10">
-        <v>13.2004348</v>
+        <v>13.08798915</v>
       </c>
       <c r="O10">
-        <v>1.98006522</v>
+        <v>1.9631983725</v>
       </c>
       <c r="P10">
-        <v>11.22036958</v>
+        <v>11.1247907775</v>
       </c>
       <c r="Q10">
-        <v>14.92036958</v>
+        <v>14.8247907775</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1081584492830693</v>
+        <v>0.1087479928374873</v>
       </c>
       <c r="T10">
-        <v>0.8583875264124795</v>
+        <v>0.866502815346174</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.67423906571753</v>
+        <v>13.93265694730447</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1028086234821134</v>
+        <v>0.1028185736238031</v>
       </c>
       <c r="C11">
-        <v>208.0563832211784</v>
+        <v>205.7817821503488</v>
       </c>
       <c r="D11">
-        <v>224.0658832211783</v>
+        <v>224.0267821503488</v>
       </c>
       <c r="E11">
-        <v>17.6695</v>
+        <v>19.905</v>
       </c>
       <c r="F11">
-        <v>20.1195</v>
+        <v>22.355</v>
       </c>
       <c r="G11">
         <v>4.11</v>
@@ -2189,45 +2189,45 @@
         <v>14.1</v>
       </c>
       <c r="M11">
-        <v>1.01201085</v>
+        <v>1.157989</v>
       </c>
       <c r="N11">
-        <v>13.08798915</v>
+        <v>12.942011</v>
       </c>
       <c r="O11">
-        <v>1.9631983725</v>
+        <v>1.94130165</v>
       </c>
       <c r="P11">
-        <v>11.1247907775</v>
+        <v>11.00070935</v>
       </c>
       <c r="Q11">
-        <v>14.8247907775</v>
+        <v>14.70070935</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1087479928374873</v>
+        <v>0.1093506373597812</v>
       </c>
       <c r="T11">
-        <v>0.866502815346174</v>
+        <v>0.8747984440339507</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.15</v>
       </c>
       <c r="W11">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.93265694730447</v>
+        <v>12.17628146726783</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1028185736238031</v>
+        <v>0.1027137737654927</v>
       </c>
       <c r="C12">
-        <v>205.7817821503488</v>
+        <v>203.9588004824458</v>
       </c>
       <c r="D12">
-        <v>224.0267821503488</v>
+        <v>224.4393004824457</v>
       </c>
       <c r="E12">
-        <v>19.905</v>
+        <v>22.1405</v>
       </c>
       <c r="F12">
-        <v>22.355</v>
+        <v>24.5905</v>
       </c>
       <c r="G12">
         <v>4.11</v>
@@ -2271,28 +2271,28 @@
         <v>14.1</v>
       </c>
       <c r="M12">
-        <v>1.157989</v>
+        <v>1.2737879</v>
       </c>
       <c r="N12">
-        <v>12.942011</v>
+        <v>12.8262121</v>
       </c>
       <c r="O12">
-        <v>1.94130165</v>
+        <v>1.923931815</v>
       </c>
       <c r="P12">
-        <v>11.00070935</v>
+        <v>10.902280285</v>
       </c>
       <c r="Q12">
-        <v>14.70070935</v>
+        <v>14.602280285</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1093506373597812</v>
+        <v>0.1099668244556098</v>
       </c>
       <c r="T12">
-        <v>0.8747984440339507</v>
+        <v>0.8832804913439245</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.17628146726782</v>
+        <v>11.06934678842529</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1027137737654927</v>
+        <v>0.1026089739071823</v>
       </c>
       <c r="C13">
-        <v>203.9588004824458</v>
+        <v>202.137340822767</v>
       </c>
       <c r="D13">
-        <v>224.4393004824457</v>
+        <v>224.853340822767</v>
       </c>
       <c r="E13">
-        <v>22.1405</v>
+        <v>24.376</v>
       </c>
       <c r="F13">
-        <v>24.5905</v>
+        <v>26.826</v>
       </c>
       <c r="G13">
         <v>4.11</v>
@@ -2353,28 +2353,28 @@
         <v>14.1</v>
       </c>
       <c r="M13">
-        <v>1.2737879</v>
+        <v>1.3895868</v>
       </c>
       <c r="N13">
-        <v>12.8262121</v>
+        <v>12.7104132</v>
       </c>
       <c r="O13">
-        <v>1.923931815</v>
+        <v>1.90656198</v>
       </c>
       <c r="P13">
-        <v>10.902280285</v>
+        <v>10.80385122</v>
       </c>
       <c r="Q13">
-        <v>14.602280285</v>
+        <v>14.50385122</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1099668244556098</v>
+        <v>0.1105970158036163</v>
       </c>
       <c r="T13">
-        <v>0.8832804913439245</v>
+        <v>0.8919553124563978</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.06934678842529</v>
+        <v>10.14690122272319</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1026089739071823</v>
+        <v>0.102692024048872</v>
       </c>
       <c r="C14">
-        <v>202.137340822767</v>
+        <v>199.5736032160565</v>
       </c>
       <c r="D14">
-        <v>224.853340822767</v>
+        <v>224.5251032160565</v>
       </c>
       <c r="E14">
-        <v>24.376</v>
+        <v>26.6115</v>
       </c>
       <c r="F14">
-        <v>26.826</v>
+        <v>29.0615</v>
       </c>
       <c r="G14">
         <v>4.11</v>
@@ -2435,45 +2435,45 @@
         <v>14.1</v>
       </c>
       <c r="M14">
-        <v>1.3895868</v>
+        <v>1.55479025</v>
       </c>
       <c r="N14">
-        <v>12.7104132</v>
+        <v>12.54520975</v>
       </c>
       <c r="O14">
-        <v>1.90656198</v>
+        <v>1.8817814625</v>
       </c>
       <c r="P14">
-        <v>10.80385122</v>
+        <v>10.6634282875</v>
       </c>
       <c r="Q14">
-        <v>14.50385122</v>
+        <v>14.3634282875</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1105970158036163</v>
+        <v>0.1112416943090483</v>
       </c>
       <c r="T14">
-        <v>0.8919553124563978</v>
+        <v>0.9008295547438704</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.15</v>
       </c>
       <c r="W14">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.14690122272319</v>
+        <v>9.068747376052816</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.102692024048872</v>
+        <v>0.1026016741905616</v>
       </c>
       <c r="C15">
-        <v>199.5736032160565</v>
+        <v>197.6952372539483</v>
       </c>
       <c r="D15">
-        <v>224.5251032160565</v>
+        <v>224.8822372539483</v>
       </c>
       <c r="E15">
-        <v>26.6115</v>
+        <v>28.847</v>
       </c>
       <c r="F15">
-        <v>29.0615</v>
+        <v>31.297</v>
       </c>
       <c r="G15">
         <v>4.11</v>
@@ -2517,28 +2517,28 @@
         <v>14.1</v>
       </c>
       <c r="M15">
-        <v>1.55479025</v>
+        <v>1.6743895</v>
       </c>
       <c r="N15">
-        <v>12.54520975</v>
+        <v>12.4256105</v>
       </c>
       <c r="O15">
-        <v>1.8817814625</v>
+        <v>1.863841575</v>
       </c>
       <c r="P15">
-        <v>10.6634282875</v>
+        <v>10.561768925</v>
       </c>
       <c r="Q15">
-        <v>14.3634282875</v>
+        <v>14.261768925</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1112416943090483</v>
+        <v>0.1119013653378624</v>
       </c>
       <c r="T15">
-        <v>0.9008295547438704</v>
+        <v>0.9099101747589586</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.068747376052816</v>
+        <v>8.420979706334755</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1026016741905616</v>
+        <v>0.1025113243322512</v>
       </c>
       <c r="C16">
-        <v>197.6952372539483</v>
+        <v>195.8180092306946</v>
       </c>
       <c r="D16">
-        <v>224.8822372539483</v>
+        <v>225.2405092306946</v>
       </c>
       <c r="E16">
-        <v>28.847</v>
+        <v>31.0825</v>
       </c>
       <c r="F16">
-        <v>31.297</v>
+        <v>33.5325</v>
       </c>
       <c r="G16">
         <v>4.11</v>
@@ -2599,28 +2599,28 @@
         <v>14.1</v>
       </c>
       <c r="M16">
-        <v>1.6743895</v>
+        <v>1.79398875</v>
       </c>
       <c r="N16">
-        <v>12.4256105</v>
+        <v>12.30601125</v>
       </c>
       <c r="O16">
-        <v>1.863841575</v>
+        <v>1.8459016875</v>
       </c>
       <c r="P16">
-        <v>10.561768925</v>
+        <v>10.4601095625</v>
       </c>
       <c r="Q16">
-        <v>14.261768925</v>
+        <v>14.1601095625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1119013653378624</v>
+        <v>0.1125765580379426</v>
       </c>
       <c r="T16">
-        <v>0.9099101747589586</v>
+        <v>0.9192044564214608</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.420979706334755</v>
+        <v>7.859581059245773</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1025113243322512</v>
+        <v>0.1025297744739409</v>
       </c>
       <c r="C17">
-        <v>195.8180092306946</v>
+        <v>193.5092545888757</v>
       </c>
       <c r="D17">
-        <v>225.2405092306946</v>
+        <v>225.1672545888757</v>
       </c>
       <c r="E17">
-        <v>31.0825</v>
+        <v>33.318</v>
       </c>
       <c r="F17">
-        <v>33.5325</v>
+        <v>35.768</v>
       </c>
       <c r="G17">
         <v>4.11</v>
@@ -2681,45 +2681,45 @@
         <v>14.1</v>
       </c>
       <c r="M17">
-        <v>1.79398875</v>
+        <v>1.9422024</v>
       </c>
       <c r="N17">
-        <v>12.30601125</v>
+        <v>12.1577976</v>
       </c>
       <c r="O17">
-        <v>1.8459016875</v>
+        <v>1.82366964</v>
       </c>
       <c r="P17">
-        <v>10.4601095625</v>
+        <v>10.33412796</v>
       </c>
       <c r="Q17">
-        <v>14.1601095625</v>
+        <v>14.03412796</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1125765580379426</v>
+        <v>0.1132678267546915</v>
       </c>
       <c r="T17">
-        <v>0.9192044564214608</v>
+        <v>0.9287200305044988</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.15</v>
       </c>
       <c r="W17">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.859581059245773</v>
+        <v>7.259799493605816</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1025297744739409</v>
+        <v>0.1024462246156305</v>
       </c>
       <c r="C18">
-        <v>193.5092545888757</v>
+        <v>191.6058630805657</v>
       </c>
       <c r="D18">
-        <v>225.1672545888757</v>
+        <v>225.4993630805657</v>
       </c>
       <c r="E18">
-        <v>33.318</v>
+        <v>35.5535</v>
       </c>
       <c r="F18">
-        <v>35.768</v>
+        <v>38.0035</v>
       </c>
       <c r="G18">
         <v>4.11</v>
@@ -2763,28 +2763,28 @@
         <v>14.1</v>
       </c>
       <c r="M18">
-        <v>1.9422024</v>
+        <v>2.06359005</v>
       </c>
       <c r="N18">
-        <v>12.1577976</v>
+        <v>12.03640995</v>
       </c>
       <c r="O18">
-        <v>1.82366964</v>
+        <v>1.8054614925</v>
       </c>
       <c r="P18">
-        <v>10.33412796</v>
+        <v>10.2309484575</v>
       </c>
       <c r="Q18">
-        <v>14.03412796</v>
+        <v>13.9309484575</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1132678267546915</v>
+        <v>0.1139757525489525</v>
       </c>
       <c r="T18">
-        <v>0.9287200305044988</v>
+        <v>0.9384648955292966</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.259799493605816</v>
+        <v>6.832752464570179</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1024462246156305</v>
+        <v>0.1023626747573202</v>
       </c>
       <c r="C19">
-        <v>191.6058630805657</v>
+        <v>189.7034527004483</v>
       </c>
       <c r="D19">
-        <v>225.4993630805657</v>
+        <v>225.8324527004483</v>
       </c>
       <c r="E19">
-        <v>35.5535</v>
+        <v>37.789</v>
       </c>
       <c r="F19">
-        <v>38.0035</v>
+        <v>40.239</v>
       </c>
       <c r="G19">
         <v>4.11</v>
@@ -2845,28 +2845,28 @@
         <v>14.1</v>
       </c>
       <c r="M19">
-        <v>2.06359005</v>
+        <v>2.1849777</v>
       </c>
       <c r="N19">
-        <v>12.03640995</v>
+        <v>11.9150223</v>
       </c>
       <c r="O19">
-        <v>1.8054614925</v>
+        <v>1.787253345</v>
       </c>
       <c r="P19">
-        <v>10.2309484575</v>
+        <v>10.127768955</v>
       </c>
       <c r="Q19">
-        <v>13.9309484575</v>
+        <v>13.827768955</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1139757525489525</v>
+        <v>0.1147009448260002</v>
       </c>
       <c r="T19">
-        <v>0.9384648955292966</v>
+        <v>0.9484474401888455</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.832752464570179</v>
+        <v>6.453155105427392</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1023626747573202</v>
+        <v>0.1022791248990098</v>
       </c>
       <c r="C20">
-        <v>189.7034527004482</v>
+        <v>187.8020278026871</v>
       </c>
       <c r="D20">
-        <v>225.8324527004482</v>
+        <v>226.1665278026871</v>
       </c>
       <c r="E20">
-        <v>37.78899999999999</v>
+        <v>40.0245</v>
       </c>
       <c r="F20">
-        <v>40.239</v>
+        <v>42.4745</v>
       </c>
       <c r="G20">
         <v>4.11</v>
@@ -2927,28 +2927,28 @@
         <v>14.1</v>
       </c>
       <c r="M20">
-        <v>2.1849777</v>
+        <v>2.30636535</v>
       </c>
       <c r="N20">
-        <v>11.9150223</v>
+        <v>11.79363465</v>
       </c>
       <c r="O20">
-        <v>1.787253345</v>
+        <v>1.7690451975</v>
       </c>
       <c r="P20">
-        <v>10.127768955</v>
+        <v>10.0245894525</v>
       </c>
       <c r="Q20">
-        <v>13.827768955</v>
+        <v>13.7245894525</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1147009448260002</v>
+        <v>0.1154440430851973</v>
       </c>
       <c r="T20">
-        <v>0.9484474401888455</v>
+        <v>0.9586764674325809</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.453155105427393</v>
+        <v>6.113515363036476</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1022791248990098</v>
+        <v>0.1023655750406995</v>
       </c>
       <c r="C21">
-        <v>187.8020278026871</v>
+        <v>185.2208736064746</v>
       </c>
       <c r="D21">
-        <v>226.1665278026871</v>
+        <v>225.8208736064746</v>
       </c>
       <c r="E21">
-        <v>40.0245</v>
+        <v>42.26</v>
       </c>
       <c r="F21">
-        <v>42.4745</v>
+        <v>44.71</v>
       </c>
       <c r="G21">
         <v>4.11</v>
@@ -3009,45 +3009,45 @@
         <v>14.1</v>
       </c>
       <c r="M21">
-        <v>2.30636535</v>
+        <v>2.472463</v>
       </c>
       <c r="N21">
-        <v>11.79363465</v>
+        <v>11.627537</v>
       </c>
       <c r="O21">
-        <v>1.7690451975</v>
+        <v>1.74413055</v>
       </c>
       <c r="P21">
-        <v>10.0245894525</v>
+        <v>9.883406450000001</v>
       </c>
       <c r="Q21">
-        <v>13.7245894525</v>
+        <v>13.58340645</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1154440430851973</v>
+        <v>0.1162057188008743</v>
       </c>
       <c r="T21">
-        <v>0.9586764674325809</v>
+        <v>0.9691612203574097</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.113515363036476</v>
+        <v>5.702815370745689</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1023655750406995</v>
+        <v>0.1022905251823891</v>
       </c>
       <c r="C22">
-        <v>185.2208736064746</v>
+        <v>183.285385413994</v>
       </c>
       <c r="D22">
-        <v>225.8208736064746</v>
+        <v>226.120885413994</v>
       </c>
       <c r="E22">
-        <v>42.26</v>
+        <v>44.4955</v>
       </c>
       <c r="F22">
-        <v>44.71</v>
+        <v>46.9455</v>
       </c>
       <c r="G22">
         <v>4.11</v>
@@ -3091,28 +3091,28 @@
         <v>14.1</v>
       </c>
       <c r="M22">
-        <v>2.472463</v>
+        <v>2.59608615</v>
       </c>
       <c r="N22">
-        <v>11.627537</v>
+        <v>11.50391385</v>
       </c>
       <c r="O22">
-        <v>1.74413055</v>
+        <v>1.7255870775</v>
       </c>
       <c r="P22">
-        <v>9.883406450000001</v>
+        <v>9.7783267725</v>
       </c>
       <c r="Q22">
-        <v>13.58340645</v>
+        <v>13.4783267725</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1162057188008743</v>
+        <v>0.1169866774460621</v>
       </c>
       <c r="T22">
-        <v>0.9691612203574097</v>
+        <v>0.9799114100651457</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.702815370745689</v>
+        <v>5.431252734043514</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1022905251823891</v>
+        <v>0.1022154753240788</v>
       </c>
       <c r="C23">
-        <v>183.285385413994</v>
+        <v>181.3506954366668</v>
       </c>
       <c r="D23">
-        <v>226.120885413994</v>
+        <v>226.4216954366668</v>
       </c>
       <c r="E23">
-        <v>44.49549999999999</v>
+        <v>46.73099999999999</v>
       </c>
       <c r="F23">
-        <v>46.9455</v>
+        <v>49.181</v>
       </c>
       <c r="G23">
         <v>4.11</v>
@@ -3173,28 +3173,28 @@
         <v>14.1</v>
       </c>
       <c r="M23">
-        <v>2.59608615</v>
+        <v>2.7197093</v>
       </c>
       <c r="N23">
-        <v>11.50391385</v>
+        <v>11.3802907</v>
       </c>
       <c r="O23">
-        <v>1.7255870775</v>
+        <v>1.707043605</v>
       </c>
       <c r="P23">
-        <v>9.7783267725</v>
+        <v>9.673247095000001</v>
       </c>
       <c r="Q23">
-        <v>13.4783267725</v>
+        <v>13.373247095</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1169866774460621</v>
+        <v>0.1177876606718958</v>
       </c>
       <c r="T23">
-        <v>0.9799114100651456</v>
+        <v>0.9909372456628235</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.431252734043515</v>
+        <v>5.184377609768809</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1022154753240788</v>
+        <v>0.1021404254657684</v>
       </c>
       <c r="C24">
-        <v>181.3506954366668</v>
+        <v>179.4168068643483</v>
       </c>
       <c r="D24">
-        <v>226.4216954366668</v>
+        <v>226.7233068643483</v>
       </c>
       <c r="E24">
-        <v>46.73099999999999</v>
+        <v>48.9665</v>
       </c>
       <c r="F24">
-        <v>49.181</v>
+        <v>51.4165</v>
       </c>
       <c r="G24">
         <v>4.11</v>
@@ -3255,28 +3255,28 @@
         <v>14.1</v>
       </c>
       <c r="M24">
-        <v>2.7197093</v>
+        <v>2.84333245</v>
       </c>
       <c r="N24">
-        <v>11.3802907</v>
+        <v>11.25666755</v>
       </c>
       <c r="O24">
-        <v>1.707043605</v>
+        <v>1.6885001325</v>
       </c>
       <c r="P24">
-        <v>9.673247095000001</v>
+        <v>9.5681674175</v>
       </c>
       <c r="Q24">
-        <v>13.373247095</v>
+        <v>13.2681674175</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1177876606718958</v>
+        <v>0.1186094486568421</v>
       </c>
       <c r="T24">
-        <v>0.9909372456628235</v>
+        <v>1.002249466600701</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.184377609768809</v>
+        <v>4.958969887604948</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1021404254657684</v>
+        <v>0.102065375607458</v>
       </c>
       <c r="C25">
-        <v>179.4168068643483</v>
+        <v>177.483722903913</v>
       </c>
       <c r="D25">
-        <v>226.7233068643483</v>
+        <v>227.025722903913</v>
       </c>
       <c r="E25">
-        <v>48.9665</v>
+        <v>51.202</v>
       </c>
       <c r="F25">
-        <v>51.4165</v>
+        <v>53.652</v>
       </c>
       <c r="G25">
         <v>4.11</v>
@@ -3337,28 +3337,28 @@
         <v>14.1</v>
       </c>
       <c r="M25">
-        <v>2.84333245</v>
+        <v>2.9669556</v>
       </c>
       <c r="N25">
-        <v>11.25666755</v>
+        <v>11.1330444</v>
       </c>
       <c r="O25">
-        <v>1.6885001325</v>
+        <v>1.66995666</v>
       </c>
       <c r="P25">
-        <v>9.5681674175</v>
+        <v>9.463087739999999</v>
       </c>
       <c r="Q25">
-        <v>13.2681674175</v>
+        <v>13.16308774</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1186094486568421</v>
+        <v>0.1194528626413921</v>
       </c>
       <c r="T25">
-        <v>1.002249466600701</v>
+        <v>1.013859377563259</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.958969887604948</v>
+        <v>4.752346142288074</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.102065375607458</v>
+        <v>0.1019903257491477</v>
       </c>
       <c r="C26">
-        <v>177.483722903913</v>
+        <v>175.5514467793682</v>
       </c>
       <c r="D26">
-        <v>227.025722903913</v>
+        <v>227.3289467793682</v>
       </c>
       <c r="E26">
-        <v>51.20199999999999</v>
+        <v>53.43749999999999</v>
       </c>
       <c r="F26">
-        <v>53.65199999999999</v>
+        <v>55.8875</v>
       </c>
       <c r="G26">
         <v>4.11</v>
@@ -3419,28 +3419,28 @@
         <v>14.1</v>
       </c>
       <c r="M26">
-        <v>2.9669556</v>
+        <v>3.09057875</v>
       </c>
       <c r="N26">
-        <v>11.1330444</v>
+        <v>11.00942125</v>
       </c>
       <c r="O26">
-        <v>1.66995666</v>
+        <v>1.6514131875</v>
       </c>
       <c r="P26">
-        <v>9.463087739999999</v>
+        <v>9.3580080625</v>
       </c>
       <c r="Q26">
-        <v>13.16308774</v>
+        <v>13.0580080625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1194528626413921</v>
+        <v>0.1203187676655302</v>
       </c>
       <c r="T26">
-        <v>1.013859377563259</v>
+        <v>1.025778886151485</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.752346142288074</v>
+        <v>4.562252296596552</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1019903257491477</v>
+        <v>0.1024677758908373</v>
       </c>
       <c r="C27">
-        <v>175.5514467793682</v>
+        <v>171.4006036033972</v>
       </c>
       <c r="D27">
-        <v>227.3289467793682</v>
+        <v>225.4136036033972</v>
       </c>
       <c r="E27">
-        <v>53.43749999999999</v>
+        <v>55.67299999999999</v>
       </c>
       <c r="F27">
-        <v>55.8875</v>
+        <v>58.123</v>
       </c>
       <c r="G27">
         <v>4.11</v>
@@ -3501,45 +3501,45 @@
         <v>14.1</v>
       </c>
       <c r="M27">
-        <v>3.09057875</v>
+        <v>3.3595094</v>
       </c>
       <c r="N27">
-        <v>11.00942125</v>
+        <v>10.7404906</v>
       </c>
       <c r="O27">
-        <v>1.6514131875</v>
+        <v>1.61107359</v>
       </c>
       <c r="P27">
-        <v>9.3580080625</v>
+        <v>9.129417009999999</v>
       </c>
       <c r="Q27">
-        <v>13.0580080625</v>
+        <v>12.82941701</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1203187676655302</v>
+        <v>0.1212080755281585</v>
       </c>
       <c r="T27">
-        <v>1.025778886151485</v>
+        <v>1.038020543620475</v>
       </c>
       <c r="U27">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V27">
         <v>0.15</v>
       </c>
       <c r="W27">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.562252296596552</v>
+        <v>4.197041389436206</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1024677758908373</v>
+        <v>0.1024139760325269</v>
       </c>
       <c r="C28">
-        <v>171.4006036033972</v>
+        <v>169.3793125458697</v>
       </c>
       <c r="D28">
-        <v>225.4136036033972</v>
+        <v>225.6278125458697</v>
       </c>
       <c r="E28">
-        <v>55.67299999999999</v>
+        <v>57.9085</v>
       </c>
       <c r="F28">
-        <v>58.123</v>
+        <v>60.3585</v>
       </c>
       <c r="G28">
         <v>4.11</v>
@@ -3583,28 +3583,28 @@
         <v>14.1</v>
       </c>
       <c r="M28">
-        <v>3.3595094</v>
+        <v>3.4887213</v>
       </c>
       <c r="N28">
-        <v>10.7404906</v>
+        <v>10.6112787</v>
       </c>
       <c r="O28">
-        <v>1.61107359</v>
+        <v>1.591691805</v>
       </c>
       <c r="P28">
-        <v>9.129417009999999</v>
+        <v>9.019586895</v>
       </c>
       <c r="Q28">
-        <v>12.82941701</v>
+        <v>12.719586895</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1212080755281585</v>
+        <v>0.1221217479897629</v>
       </c>
       <c r="T28">
-        <v>1.038020543620475</v>
+        <v>1.050597588965327</v>
       </c>
       <c r="U28">
         <v>0.0578</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.197041389436206</v>
+        <v>4.041595412049681</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1024139760325269</v>
+        <v>0.1031931761742166</v>
       </c>
       <c r="C29">
-        <v>169.3793125458697</v>
+        <v>164.0805699232415</v>
       </c>
       <c r="D29">
-        <v>225.6278125458697</v>
+        <v>222.5645699232415</v>
       </c>
       <c r="E29">
-        <v>57.9085</v>
+        <v>60.144</v>
       </c>
       <c r="F29">
-        <v>60.3585</v>
+        <v>62.594</v>
       </c>
       <c r="G29">
         <v>4.11</v>
@@ -3665,45 +3665,45 @@
         <v>14.1</v>
       </c>
       <c r="M29">
-        <v>3.4887213</v>
+        <v>3.8370122</v>
       </c>
       <c r="N29">
-        <v>10.6112787</v>
+        <v>10.2629878</v>
       </c>
       <c r="O29">
-        <v>1.591691805</v>
+        <v>1.53944817</v>
       </c>
       <c r="P29">
-        <v>9.019586895</v>
+        <v>8.723539629999999</v>
       </c>
       <c r="Q29">
-        <v>12.719586895</v>
+        <v>12.42353963</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1221217479897629</v>
+        <v>0.1230608002419675</v>
       </c>
       <c r="T29">
-        <v>1.050597588965327</v>
+        <v>1.063523996680869</v>
       </c>
       <c r="U29">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V29">
         <v>0.15</v>
       </c>
       <c r="W29">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.041595412049681</v>
+        <v>3.674734211165656</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1031931761742166</v>
+        <v>0.1031691263159062</v>
       </c>
       <c r="C30">
-        <v>164.0805699232415</v>
+        <v>161.9383717863741</v>
       </c>
       <c r="D30">
-        <v>222.5645699232415</v>
+        <v>222.6578717863741</v>
       </c>
       <c r="E30">
-        <v>60.144</v>
+        <v>62.37949999999999</v>
       </c>
       <c r="F30">
-        <v>62.594</v>
+        <v>64.8295</v>
       </c>
       <c r="G30">
         <v>4.11</v>
@@ -3747,28 +3747,28 @@
         <v>14.1</v>
       </c>
       <c r="M30">
-        <v>3.8370122</v>
+        <v>3.97404835</v>
       </c>
       <c r="N30">
-        <v>10.2629878</v>
+        <v>10.12595165</v>
       </c>
       <c r="O30">
-        <v>1.53944817</v>
+        <v>1.5188927475</v>
       </c>
       <c r="P30">
-        <v>8.723539629999999</v>
+        <v>8.6070589025</v>
       </c>
       <c r="Q30">
-        <v>12.42353963</v>
+        <v>12.3070589025</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1230608002419675</v>
+        <v>0.1240263046702905</v>
       </c>
       <c r="T30">
-        <v>1.063523996680869</v>
+        <v>1.076814528557413</v>
       </c>
       <c r="U30">
         <v>0.0613</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.674734211165656</v>
+        <v>3.548019238366841</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1031691263159062</v>
+        <v>0.1038590764575959</v>
       </c>
       <c r="C31">
-        <v>161.9383717863741</v>
+        <v>157.056897383052</v>
       </c>
       <c r="D31">
-        <v>222.6578717863741</v>
+        <v>220.011897383052</v>
       </c>
       <c r="E31">
-        <v>62.37949999999999</v>
+        <v>64.61499999999999</v>
       </c>
       <c r="F31">
-        <v>64.8295</v>
+        <v>67.065</v>
       </c>
       <c r="G31">
         <v>4.11</v>
@@ -3829,45 +3829,45 @@
         <v>14.1</v>
       </c>
       <c r="M31">
-        <v>3.97404835</v>
+        <v>4.2988665</v>
       </c>
       <c r="N31">
-        <v>10.12595165</v>
+        <v>9.801133499999999</v>
       </c>
       <c r="O31">
-        <v>1.5188927475</v>
+        <v>1.470170025</v>
       </c>
       <c r="P31">
-        <v>8.6070589025</v>
+        <v>8.330963474999999</v>
       </c>
       <c r="Q31">
-        <v>12.3070589025</v>
+        <v>12.030963475</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1240263046702905</v>
+        <v>0.1250193949394227</v>
       </c>
       <c r="T31">
-        <v>1.076814528557413</v>
+        <v>1.090484789916143</v>
       </c>
       <c r="U31">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V31">
         <v>0.15</v>
       </c>
       <c r="W31">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>3.548019238366841</v>
+        <v>3.279934373398197</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1038590764575959</v>
+        <v>0.1038588265992855</v>
       </c>
       <c r="C32">
-        <v>157.056897383052</v>
+        <v>154.8223442124001</v>
       </c>
       <c r="D32">
-        <v>220.011897383052</v>
+        <v>220.0128442124001</v>
       </c>
       <c r="E32">
-        <v>64.61499999999999</v>
+        <v>66.8505</v>
       </c>
       <c r="F32">
-        <v>67.065</v>
+        <v>69.3005</v>
       </c>
       <c r="G32">
         <v>4.11</v>
@@ -3911,28 +3911,28 @@
         <v>14.1</v>
       </c>
       <c r="M32">
-        <v>4.2988665</v>
+        <v>4.44216205</v>
       </c>
       <c r="N32">
-        <v>9.801133499999999</v>
+        <v>9.657837949999999</v>
       </c>
       <c r="O32">
-        <v>1.470170025</v>
+        <v>1.4486756925</v>
       </c>
       <c r="P32">
-        <v>8.330963474999999</v>
+        <v>8.209162257499999</v>
       </c>
       <c r="Q32">
-        <v>12.030963475</v>
+        <v>11.9091622575</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1250193949394227</v>
+        <v>0.1260412704337471</v>
       </c>
       <c r="T32">
-        <v>1.090484789916143</v>
+        <v>1.104551290734547</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.279934373398197</v>
+        <v>3.174130038772448</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1038588265992855</v>
+        <v>0.1038585767409751</v>
       </c>
       <c r="C33">
-        <v>154.8223442124001</v>
+        <v>152.5877910498977</v>
       </c>
       <c r="D33">
-        <v>220.0128442124001</v>
+        <v>220.0137910498977</v>
       </c>
       <c r="E33">
-        <v>66.8505</v>
+        <v>69.086</v>
       </c>
       <c r="F33">
-        <v>69.3005</v>
+        <v>71.536</v>
       </c>
       <c r="G33">
         <v>4.11</v>
@@ -3993,28 +3993,28 @@
         <v>14.1</v>
       </c>
       <c r="M33">
-        <v>4.44216205</v>
+        <v>4.585457600000001</v>
       </c>
       <c r="N33">
-        <v>9.657837949999999</v>
+        <v>9.5145424</v>
       </c>
       <c r="O33">
-        <v>1.4486756925</v>
+        <v>1.42718136</v>
       </c>
       <c r="P33">
-        <v>8.209162257499999</v>
+        <v>8.087361039999999</v>
       </c>
       <c r="Q33">
-        <v>11.9091622575</v>
+        <v>11.78736104</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1260412704337471</v>
+        <v>0.1270932010896693</v>
       </c>
       <c r="T33">
-        <v>1.104551290734547</v>
+        <v>1.119031512165257</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.174130038772448</v>
+        <v>3.074938475060809</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1038585767409751</v>
+        <v>0.1060462268826648</v>
       </c>
       <c r="C34">
-        <v>152.5877910498977</v>
+        <v>142.3631898884027</v>
       </c>
       <c r="D34">
-        <v>220.0137910498977</v>
+        <v>212.0246898884027</v>
       </c>
       <c r="E34">
-        <v>69.086</v>
+        <v>71.3215</v>
       </c>
       <c r="F34">
-        <v>71.536</v>
+        <v>73.7715</v>
       </c>
       <c r="G34">
         <v>4.11</v>
@@ -4075,45 +4075,45 @@
         <v>14.1</v>
       </c>
       <c r="M34">
-        <v>4.585457600000001</v>
+        <v>5.30417085</v>
       </c>
       <c r="N34">
-        <v>9.5145424</v>
+        <v>8.795829149999999</v>
       </c>
       <c r="O34">
-        <v>1.42718136</v>
+        <v>1.3193743725</v>
       </c>
       <c r="P34">
-        <v>8.087361039999999</v>
+        <v>7.4764547775</v>
       </c>
       <c r="Q34">
-        <v>11.78736104</v>
+        <v>11.1764547775</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1270932010896693</v>
+        <v>0.1281765326606937</v>
       </c>
       <c r="T34">
-        <v>1.119031512165257</v>
+        <v>1.133943979011809</v>
       </c>
       <c r="U34">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V34">
         <v>0.15</v>
       </c>
       <c r="W34">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.074938475060809</v>
+        <v>2.658285413261151</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1060462268826648</v>
+        <v>0.1061122770243544</v>
       </c>
       <c r="C35">
-        <v>142.3631898884027</v>
+        <v>139.8954940321067</v>
       </c>
       <c r="D35">
-        <v>212.0246898884027</v>
+        <v>211.7924940321067</v>
       </c>
       <c r="E35">
-        <v>71.3215</v>
+        <v>73.557</v>
       </c>
       <c r="F35">
-        <v>73.7715</v>
+        <v>76.00700000000001</v>
       </c>
       <c r="G35">
         <v>4.11</v>
@@ -4157,28 +4157,28 @@
         <v>14.1</v>
       </c>
       <c r="M35">
-        <v>5.30417085</v>
+        <v>5.4649033</v>
       </c>
       <c r="N35">
-        <v>8.795829149999999</v>
+        <v>8.635096699999998</v>
       </c>
       <c r="O35">
-        <v>1.3193743725</v>
+        <v>1.295264505</v>
       </c>
       <c r="P35">
-        <v>7.4764547775</v>
+        <v>7.339832194999999</v>
       </c>
       <c r="Q35">
-        <v>11.1764547775</v>
+        <v>11.039832195</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1281765326606937</v>
+        <v>0.1292926924611431</v>
       </c>
       <c r="T35">
-        <v>1.133943979011809</v>
+        <v>1.149308338793105</v>
       </c>
       <c r="U35">
         <v>0.07190000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.658285413261151</v>
+        <v>2.580100548165234</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1061122770243544</v>
+        <v>0.1061783271660441</v>
       </c>
       <c r="C36">
-        <v>139.8954940321067</v>
+        <v>137.4283061915153</v>
       </c>
       <c r="D36">
-        <v>211.7924940321067</v>
+        <v>211.5608061915153</v>
       </c>
       <c r="E36">
-        <v>73.557</v>
+        <v>75.7925</v>
       </c>
       <c r="F36">
-        <v>76.00700000000001</v>
+        <v>78.24250000000001</v>
       </c>
       <c r="G36">
         <v>4.11</v>
@@ -4239,28 +4239,28 @@
         <v>14.1</v>
       </c>
       <c r="M36">
-        <v>5.4649033</v>
+        <v>5.625635750000001</v>
       </c>
       <c r="N36">
-        <v>8.635096699999998</v>
+        <v>8.474364249999999</v>
       </c>
       <c r="O36">
-        <v>1.295264505</v>
+        <v>1.2711546375</v>
       </c>
       <c r="P36">
-        <v>7.339832194999999</v>
+        <v>7.203209612499999</v>
       </c>
       <c r="Q36">
-        <v>11.039832195</v>
+        <v>10.9032096125</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1292926924611431</v>
+        <v>0.1304431956400678</v>
       </c>
       <c r="T36">
-        <v>1.149308338793105</v>
+        <v>1.165145448106133</v>
       </c>
       <c r="U36">
         <v>0.07190000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.580100548165234</v>
+        <v>2.506383389646228</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1061783271660441</v>
+        <v>0.1074377773077337</v>
       </c>
       <c r="C37">
-        <v>137.4283061915153</v>
+        <v>130.8699655737624</v>
       </c>
       <c r="D37">
-        <v>211.5608061915153</v>
+        <v>207.2379655737624</v>
       </c>
       <c r="E37">
-        <v>75.7925</v>
+        <v>78.02800000000001</v>
       </c>
       <c r="F37">
-        <v>78.24250000000001</v>
+        <v>80.47800000000001</v>
       </c>
       <c r="G37">
         <v>4.11</v>
@@ -4321,45 +4321,45 @@
         <v>14.1</v>
       </c>
       <c r="M37">
-        <v>5.625635750000001</v>
+        <v>6.100232400000001</v>
       </c>
       <c r="N37">
-        <v>8.474364249999999</v>
+        <v>7.999767599999998</v>
       </c>
       <c r="O37">
-        <v>1.2711546375</v>
+        <v>1.19996514</v>
       </c>
       <c r="P37">
-        <v>7.203209612499999</v>
+        <v>6.799802459999999</v>
       </c>
       <c r="Q37">
-        <v>10.9032096125</v>
+        <v>10.49980246</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1304431956400678</v>
+        <v>0.1316296520433339</v>
       </c>
       <c r="T37">
-        <v>1.165145448106133</v>
+        <v>1.181477467085193</v>
       </c>
       <c r="U37">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V37">
         <v>0.15</v>
       </c>
       <c r="W37">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.506383389646228</v>
+        <v>2.311387349767199</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1074377773077337</v>
+        <v>0.1075369774494233</v>
       </c>
       <c r="C38">
-        <v>130.8699655737624</v>
+        <v>128.301471695576</v>
       </c>
       <c r="D38">
-        <v>207.2379655737624</v>
+        <v>206.904971695576</v>
       </c>
       <c r="E38">
-        <v>78.02799999999999</v>
+        <v>80.26349999999999</v>
       </c>
       <c r="F38">
-        <v>80.47799999999999</v>
+        <v>82.7135</v>
       </c>
       <c r="G38">
         <v>4.11</v>
@@ -4403,28 +4403,28 @@
         <v>14.1</v>
       </c>
       <c r="M38">
-        <v>6.1002324</v>
+        <v>6.269683300000001</v>
       </c>
       <c r="N38">
-        <v>7.999767599999999</v>
+        <v>7.830316699999999</v>
       </c>
       <c r="O38">
-        <v>1.19996514</v>
+        <v>1.174547505</v>
       </c>
       <c r="P38">
-        <v>6.79980246</v>
+        <v>6.655769195</v>
       </c>
       <c r="Q38">
-        <v>10.49980246</v>
+        <v>10.355769195</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1316296520433339</v>
+        <v>0.1328537737292434</v>
       </c>
       <c r="T38">
-        <v>1.181477467085193</v>
+        <v>1.198327962857239</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.311387349767199</v>
+        <v>2.248917421395112</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1075369774494233</v>
+        <v>0.107636177591113</v>
       </c>
       <c r="C39">
-        <v>128.301471695576</v>
+        <v>125.734046222365</v>
       </c>
       <c r="D39">
-        <v>206.904971695576</v>
+        <v>206.573046222365</v>
       </c>
       <c r="E39">
-        <v>80.26349999999999</v>
+        <v>82.499</v>
       </c>
       <c r="F39">
-        <v>82.7135</v>
+        <v>84.949</v>
       </c>
       <c r="G39">
         <v>4.11</v>
@@ -4485,28 +4485,28 @@
         <v>14.1</v>
       </c>
       <c r="M39">
-        <v>6.269683300000001</v>
+        <v>6.439134200000001</v>
       </c>
       <c r="N39">
-        <v>7.830316699999999</v>
+        <v>7.660865799999999</v>
       </c>
       <c r="O39">
-        <v>1.174547505</v>
+        <v>1.14912987</v>
       </c>
       <c r="P39">
-        <v>6.655769195</v>
+        <v>6.511735929999999</v>
       </c>
       <c r="Q39">
-        <v>10.355769195</v>
+        <v>10.21173593</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1328537737292434</v>
+        <v>0.1341173832114725</v>
       </c>
       <c r="T39">
-        <v>1.198327962857239</v>
+        <v>1.215722023009029</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.248917421395112</v>
+        <v>2.189735383989978</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.107636177591113</v>
+        <v>0.1077353777328026</v>
       </c>
       <c r="C40">
-        <v>125.734046222365</v>
+        <v>123.1676840204273</v>
       </c>
       <c r="D40">
-        <v>206.573046222365</v>
+        <v>206.2421840204273</v>
       </c>
       <c r="E40">
-        <v>82.499</v>
+        <v>84.7345</v>
       </c>
       <c r="F40">
-        <v>84.949</v>
+        <v>87.1845</v>
       </c>
       <c r="G40">
         <v>4.11</v>
@@ -4567,28 +4567,28 @@
         <v>14.1</v>
       </c>
       <c r="M40">
-        <v>6.439134200000001</v>
+        <v>6.608585100000001</v>
       </c>
       <c r="N40">
-        <v>7.660865799999999</v>
+        <v>7.491414899999999</v>
       </c>
       <c r="O40">
-        <v>1.14912987</v>
+        <v>1.123712235</v>
       </c>
       <c r="P40">
-        <v>6.511735929999999</v>
+        <v>6.367702664999999</v>
       </c>
       <c r="Q40">
-        <v>10.21173593</v>
+        <v>10.067702665</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1341173832114725</v>
+        <v>0.1354224225127912</v>
       </c>
       <c r="T40">
-        <v>1.215722023009029</v>
+        <v>1.233686380214976</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.189735383989978</v>
+        <v>2.13358832286203</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1077353777328026</v>
+        <v>0.1078345778744923</v>
       </c>
       <c r="C41">
-        <v>123.1676840204273</v>
+        <v>120.6023799888982</v>
       </c>
       <c r="D41">
-        <v>206.2421840204273</v>
+        <v>205.9123799888982</v>
       </c>
       <c r="E41">
-        <v>84.7345</v>
+        <v>86.97</v>
       </c>
       <c r="F41">
-        <v>87.1845</v>
+        <v>89.42</v>
       </c>
       <c r="G41">
         <v>4.11</v>
@@ -4649,28 +4649,28 @@
         <v>14.1</v>
       </c>
       <c r="M41">
-        <v>6.608585100000001</v>
+        <v>6.778036000000001</v>
       </c>
       <c r="N41">
-        <v>7.491414899999999</v>
+        <v>7.321963999999999</v>
       </c>
       <c r="O41">
-        <v>1.123712235</v>
+        <v>1.0982946</v>
       </c>
       <c r="P41">
-        <v>6.367702664999999</v>
+        <v>6.223669399999999</v>
       </c>
       <c r="Q41">
-        <v>10.067702665</v>
+        <v>9.9236694</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1354224225127912</v>
+        <v>0.1367709631241538</v>
       </c>
       <c r="T41">
-        <v>1.233686380214976</v>
+        <v>1.252249549327787</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.13358832286203</v>
+        <v>2.080248614790479</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1078345778744923</v>
+        <v>0.1079337780161819</v>
       </c>
       <c r="C42">
-        <v>120.6023799888982</v>
+        <v>118.0381290594887</v>
       </c>
       <c r="D42">
-        <v>205.9123799888982</v>
+        <v>205.5836290594887</v>
       </c>
       <c r="E42">
-        <v>86.97</v>
+        <v>89.2055</v>
       </c>
       <c r="F42">
-        <v>89.42</v>
+        <v>91.6555</v>
       </c>
       <c r="G42">
         <v>4.11</v>
@@ -4731,28 +4731,28 @@
         <v>14.1</v>
       </c>
       <c r="M42">
-        <v>6.778036000000001</v>
+        <v>6.947486900000001</v>
       </c>
       <c r="N42">
-        <v>7.321963999999999</v>
+        <v>7.152513099999998</v>
       </c>
       <c r="O42">
-        <v>1.0982946</v>
+        <v>1.072876965</v>
       </c>
       <c r="P42">
-        <v>6.223669399999999</v>
+        <v>6.079636134999999</v>
       </c>
       <c r="Q42">
-        <v>9.9236694</v>
+        <v>9.779636135000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1367709631241538</v>
+        <v>0.1381652169765795</v>
       </c>
       <c r="T42">
-        <v>1.252249549327787</v>
+        <v>1.271441978410525</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.080248614790479</v>
+        <v>2.029510843698028</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1079337780161819</v>
+        <v>0.1131023781578715</v>
       </c>
       <c r="C43">
-        <v>118.0381290594887</v>
+        <v>100.0144860046705</v>
       </c>
       <c r="D43">
-        <v>205.5836290594887</v>
+        <v>189.7954860046705</v>
       </c>
       <c r="E43">
-        <v>89.2055</v>
+        <v>91.441</v>
       </c>
       <c r="F43">
-        <v>91.6555</v>
+        <v>93.89100000000001</v>
       </c>
       <c r="G43">
         <v>4.11</v>
@@ -4813,45 +4813,45 @@
         <v>14.1</v>
       </c>
       <c r="M43">
-        <v>6.947486900000001</v>
+        <v>8.450190000000001</v>
       </c>
       <c r="N43">
-        <v>7.152513099999998</v>
+        <v>5.649809999999999</v>
       </c>
       <c r="O43">
-        <v>1.072876965</v>
+        <v>0.8474714999999998</v>
       </c>
       <c r="P43">
-        <v>6.079636134999999</v>
+        <v>4.802338499999999</v>
       </c>
       <c r="Q43">
-        <v>9.779636135000001</v>
+        <v>8.5023385</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1381652169765795</v>
+        <v>0.1396075485480544</v>
       </c>
       <c r="T43">
-        <v>1.271441978410525</v>
+        <v>1.291296215392667</v>
       </c>
       <c r="U43">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V43">
         <v>0.15</v>
       </c>
       <c r="W43">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.029510843698028</v>
+        <v>1.668601534403368</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1131023781578716</v>
+        <v>0.1133222782995612</v>
       </c>
       <c r="C44">
-        <v>100.0144860046705</v>
+        <v>97.16087809546579</v>
       </c>
       <c r="D44">
-        <v>189.7954860046705</v>
+        <v>189.1773780954658</v>
       </c>
       <c r="E44">
-        <v>91.44099999999999</v>
+        <v>93.67649999999999</v>
       </c>
       <c r="F44">
-        <v>93.89099999999999</v>
+        <v>96.12649999999999</v>
       </c>
       <c r="G44">
         <v>4.11</v>
@@ -4895,28 +4895,28 @@
         <v>14.1</v>
       </c>
       <c r="M44">
-        <v>8.450189999999999</v>
+        <v>8.651384999999999</v>
       </c>
       <c r="N44">
-        <v>5.64981</v>
+        <v>5.448615</v>
       </c>
       <c r="O44">
-        <v>0.8474715</v>
+        <v>0.8172922500000001</v>
       </c>
       <c r="P44">
-        <v>4.8023385</v>
+        <v>4.63132275</v>
       </c>
       <c r="Q44">
-        <v>8.5023385</v>
+        <v>8.331322750000002</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1396075485480544</v>
+        <v>0.1411004882448442</v>
       </c>
       <c r="T44">
-        <v>1.291296215392667</v>
+        <v>1.311847092268919</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.668601534403368</v>
+        <v>1.629796847556779</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1133222782995612</v>
+        <v>0.1135421784412508</v>
       </c>
       <c r="C45">
-        <v>97.16087809546579</v>
+        <v>94.31128310760315</v>
       </c>
       <c r="D45">
-        <v>189.1773780954658</v>
+        <v>188.5632831076031</v>
       </c>
       <c r="E45">
-        <v>93.67649999999999</v>
+        <v>95.91199999999999</v>
       </c>
       <c r="F45">
-        <v>96.12649999999999</v>
+        <v>98.36199999999999</v>
       </c>
       <c r="G45">
         <v>4.11</v>
@@ -4977,28 +4977,28 @@
         <v>14.1</v>
       </c>
       <c r="M45">
-        <v>8.651384999999999</v>
+        <v>8.85258</v>
       </c>
       <c r="N45">
-        <v>5.448615</v>
+        <v>5.24742</v>
       </c>
       <c r="O45">
-        <v>0.8172922500000001</v>
+        <v>0.787113</v>
       </c>
       <c r="P45">
-        <v>4.63132275</v>
+        <v>4.460307</v>
       </c>
       <c r="Q45">
-        <v>8.331322750000002</v>
+        <v>8.160307000000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1411004882448442</v>
+        <v>0.1426467472165193</v>
       </c>
       <c r="T45">
-        <v>1.311847092268919</v>
+        <v>1.333131929033609</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.629796847556779</v>
+        <v>1.592756010112306</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1135421784412508</v>
+        <v>0.1137620785829404</v>
       </c>
       <c r="C46">
-        <v>94.31128310760315</v>
+        <v>91.46566208809642</v>
       </c>
       <c r="D46">
-        <v>188.5632831076031</v>
+        <v>187.9531620880964</v>
       </c>
       <c r="E46">
-        <v>95.91199999999999</v>
+        <v>98.14749999999999</v>
       </c>
       <c r="F46">
-        <v>98.36199999999999</v>
+        <v>100.5975</v>
       </c>
       <c r="G46">
         <v>4.11</v>
@@ -5059,28 +5059,28 @@
         <v>14.1</v>
       </c>
       <c r="M46">
-        <v>8.85258</v>
+        <v>9.053775</v>
       </c>
       <c r="N46">
-        <v>5.24742</v>
+        <v>5.046225</v>
       </c>
       <c r="O46">
-        <v>0.787113</v>
+        <v>0.75693375</v>
       </c>
       <c r="P46">
-        <v>4.460307</v>
+        <v>4.28929125</v>
       </c>
       <c r="Q46">
-        <v>8.160307000000001</v>
+        <v>7.989291250000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1426467472165193</v>
+        <v>0.1442492337871644</v>
       </c>
       <c r="T46">
-        <v>1.333131929033609</v>
+        <v>1.35519075986247</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.592756010112306</v>
+        <v>1.55736143210981</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1137620785829404</v>
+        <v>0.1139819787246301</v>
       </c>
       <c r="C47">
-        <v>91.46566208809642</v>
+        <v>88.62397658648288</v>
       </c>
       <c r="D47">
-        <v>187.9531620880964</v>
+        <v>187.3469765864829</v>
       </c>
       <c r="E47">
-        <v>98.14749999999999</v>
+        <v>100.383</v>
       </c>
       <c r="F47">
-        <v>100.5975</v>
+        <v>102.833</v>
       </c>
       <c r="G47">
         <v>4.11</v>
@@ -5141,28 +5141,28 @@
         <v>14.1</v>
       </c>
       <c r="M47">
-        <v>9.053775</v>
+        <v>9.25497</v>
       </c>
       <c r="N47">
-        <v>5.046225</v>
+        <v>4.84503</v>
       </c>
       <c r="O47">
-        <v>0.75693375</v>
+        <v>0.7267544999999999</v>
       </c>
       <c r="P47">
-        <v>4.28929125</v>
+        <v>4.118275499999999</v>
       </c>
       <c r="Q47">
-        <v>7.989291250000001</v>
+        <v>7.8182755</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1442492337871644</v>
+        <v>0.145911071712278</v>
       </c>
       <c r="T47">
-        <v>1.35519075986247</v>
+        <v>1.378066584425733</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.55736143210981</v>
+        <v>1.523505748803075</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1139819787246301</v>
+        <v>0.1381333253603622</v>
       </c>
       <c r="C48">
-        <v>88.62397658648288</v>
+        <v>37.38469864349827</v>
       </c>
       <c r="D48">
-        <v>187.3469765864829</v>
+        <v>138.3431986434983</v>
       </c>
       <c r="E48">
-        <v>100.383</v>
+        <v>102.6185</v>
       </c>
       <c r="F48">
-        <v>102.833</v>
+        <v>105.0685</v>
       </c>
       <c r="G48">
         <v>4.11</v>
@@ -5223,45 +5223,45 @@
         <v>14.1</v>
       </c>
       <c r="M48">
-        <v>9.25497</v>
+        <v>15.4240558</v>
       </c>
       <c r="N48">
-        <v>4.84503</v>
+        <v>-1.324055800000002</v>
       </c>
       <c r="O48">
-        <v>0.7267544999999999</v>
+        <v>-0.1986083700000003</v>
       </c>
       <c r="P48">
-        <v>4.118275499999999</v>
+        <v>-1.125447430000001</v>
       </c>
       <c r="Q48">
-        <v>7.8182755</v>
+        <v>2.57455257</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.145911071712278</v>
+        <v>0.1482986718121308</v>
       </c>
       <c r="T48">
-        <v>1.378066584425733</v>
+        <v>1.410932798504781</v>
       </c>
       <c r="U48">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.15</v>
+        <v>0.1371234665787451</v>
       </c>
       <c r="W48">
-        <v>0.0765</v>
+        <v>0.1266702751062402</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.523505748803075</v>
+        <v>0.9141564438583007</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1381333253603622</v>
+        <v>0.1391433253603622</v>
       </c>
       <c r="C49">
-        <v>37.38469864349827</v>
+        <v>33.65228785646019</v>
       </c>
       <c r="D49">
-        <v>138.3431986434983</v>
+        <v>136.8462878564602</v>
       </c>
       <c r="E49">
-        <v>102.6185</v>
+        <v>104.854</v>
       </c>
       <c r="F49">
-        <v>105.0685</v>
+        <v>107.304</v>
       </c>
       <c r="G49">
         <v>4.11</v>
@@ -5305,37 +5305,37 @@
         <v>14.1</v>
       </c>
       <c r="M49">
-        <v>15.4240558</v>
+        <v>15.7522272</v>
       </c>
       <c r="N49">
-        <v>-1.324055800000002</v>
+        <v>-1.652227200000002</v>
       </c>
       <c r="O49">
-        <v>-0.1986083700000003</v>
+        <v>-0.2478340800000003</v>
       </c>
       <c r="P49">
-        <v>-1.125447430000001</v>
+        <v>-1.404393120000002</v>
       </c>
       <c r="Q49">
-        <v>2.57455257</v>
+        <v>2.295606879999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1482986718121308</v>
+        <v>0.1502698001162102</v>
       </c>
       <c r="T49">
-        <v>1.410932798504781</v>
+        <v>1.43806612155295</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1371234665787451</v>
+        <v>0.1342667276916879</v>
       </c>
       <c r="W49">
-        <v>0.1266702751062402</v>
+        <v>0.1270896443748602</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.9141564438583007</v>
+        <v>0.8951115179445861</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1391433253603622</v>
+        <v>0.1401533253603622</v>
       </c>
       <c r="C50">
-        <v>33.65228785646021</v>
+        <v>29.95192426837632</v>
       </c>
       <c r="D50">
-        <v>136.8462878564602</v>
+        <v>135.3814242683763</v>
       </c>
       <c r="E50">
-        <v>104.854</v>
+        <v>107.0895</v>
       </c>
       <c r="F50">
-        <v>107.304</v>
+        <v>109.5395</v>
       </c>
       <c r="G50">
         <v>4.11</v>
@@ -5387,37 +5387,37 @@
         <v>14.1</v>
       </c>
       <c r="M50">
-        <v>15.7522272</v>
+        <v>16.0803986</v>
       </c>
       <c r="N50">
-        <v>-1.6522272</v>
+        <v>-1.980398599999999</v>
       </c>
       <c r="O50">
-        <v>-0.2478340800000001</v>
+        <v>-0.2970597899999999</v>
       </c>
       <c r="P50">
-        <v>-1.40439312</v>
+        <v>-1.683338809999999</v>
       </c>
       <c r="Q50">
-        <v>2.295606880000001</v>
+        <v>2.016661190000002</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1502698001162102</v>
+        <v>0.1523182275694693</v>
       </c>
       <c r="T50">
-        <v>1.43806612155295</v>
+        <v>1.466263496485361</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.1342667276916879</v>
+        <v>0.1315265903918576</v>
       </c>
       <c r="W50">
-        <v>0.1270896443748602</v>
+        <v>0.1274918965304753</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8951115179445862</v>
+        <v>0.8768439359457172</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1401533253603622</v>
+        <v>0.1411633253603622</v>
       </c>
       <c r="C51">
-        <v>29.95192426837632</v>
+        <v>26.28258963651591</v>
       </c>
       <c r="D51">
-        <v>135.3814242683763</v>
+        <v>133.9475896365159</v>
       </c>
       <c r="E51">
-        <v>107.0895</v>
+        <v>109.325</v>
       </c>
       <c r="F51">
-        <v>109.5395</v>
+        <v>111.775</v>
       </c>
       <c r="G51">
         <v>4.11</v>
@@ -5469,37 +5469,37 @@
         <v>14.1</v>
       </c>
       <c r="M51">
-        <v>16.0803986</v>
+        <v>16.40857</v>
       </c>
       <c r="N51">
-        <v>-1.980398599999999</v>
+        <v>-2.308570000000001</v>
       </c>
       <c r="O51">
-        <v>-0.2970597899999999</v>
+        <v>-0.3462855000000002</v>
       </c>
       <c r="P51">
-        <v>-1.683338809999999</v>
+        <v>-1.962284500000001</v>
       </c>
       <c r="Q51">
-        <v>2.016661190000002</v>
+        <v>1.7377155</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1523182275694693</v>
+        <v>0.1544485921208586</v>
       </c>
       <c r="T51">
-        <v>1.466263496485361</v>
+        <v>1.495588766415068</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.1315265903918576</v>
+        <v>0.1288960585840204</v>
       </c>
       <c r="W51">
-        <v>0.1274918965304753</v>
+        <v>0.1278780585998658</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8768439359457172</v>
+        <v>0.8593070572268028</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1411633253603622</v>
+        <v>0.1421733253603622</v>
       </c>
       <c r="C52">
-        <v>26.28258963651591</v>
+        <v>22.64330840320251</v>
       </c>
       <c r="D52">
-        <v>133.9475896365159</v>
+        <v>132.5438084032025</v>
       </c>
       <c r="E52">
-        <v>109.325</v>
+        <v>111.5605</v>
       </c>
       <c r="F52">
-        <v>111.775</v>
+        <v>114.0105</v>
       </c>
       <c r="G52">
         <v>4.11</v>
@@ -5551,37 +5551,37 @@
         <v>14.1</v>
       </c>
       <c r="M52">
-        <v>16.40857</v>
+        <v>16.7367414</v>
       </c>
       <c r="N52">
-        <v>-2.308570000000001</v>
+        <v>-2.6367414</v>
       </c>
       <c r="O52">
-        <v>-0.3462855000000002</v>
+        <v>-0.39551121</v>
       </c>
       <c r="P52">
-        <v>-1.962284500000001</v>
+        <v>-2.24123019</v>
       </c>
       <c r="Q52">
-        <v>1.7377155</v>
+        <v>1.458769810000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1544485921208586</v>
+        <v>0.1566659103274068</v>
       </c>
       <c r="T52">
-        <v>1.495588766415068</v>
+        <v>1.526110986137825</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.1288960585840204</v>
+        <v>0.1263686848862945</v>
       </c>
       <c r="W52">
-        <v>0.1278780585998658</v>
+        <v>0.128249077058692</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8593070572268028</v>
+        <v>0.8424578992419636</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1421733253603622</v>
+        <v>0.1431833253603622</v>
       </c>
       <c r="C53">
-        <v>22.64330840320251</v>
+        <v>19.03314548229842</v>
       </c>
       <c r="D53">
-        <v>132.5438084032025</v>
+        <v>131.1691454822984</v>
       </c>
       <c r="E53">
-        <v>111.5605</v>
+        <v>113.796</v>
       </c>
       <c r="F53">
-        <v>114.0105</v>
+        <v>116.246</v>
       </c>
       <c r="G53">
         <v>4.11</v>
@@ -5633,37 +5633,37 @@
         <v>14.1</v>
       </c>
       <c r="M53">
-        <v>16.7367414</v>
+        <v>17.0649128</v>
       </c>
       <c r="N53">
-        <v>-2.6367414</v>
+        <v>-2.964912800000002</v>
       </c>
       <c r="O53">
-        <v>-0.39551121</v>
+        <v>-0.4447369200000003</v>
       </c>
       <c r="P53">
-        <v>-2.24123019</v>
+        <v>-2.520175880000002</v>
       </c>
       <c r="Q53">
-        <v>1.458769810000001</v>
+        <v>1.179824119999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1566659103274068</v>
+        <v>0.1589756167925611</v>
       </c>
       <c r="T53">
-        <v>1.526110986137825</v>
+        <v>1.557904965015696</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1263686848862945</v>
+        <v>0.1239385178692504</v>
       </c>
       <c r="W53">
-        <v>0.128249077058692</v>
+        <v>0.1286058255767941</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8424578992419636</v>
+        <v>0.8262567857950026</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1431833253603622</v>
+        <v>0.1441933253603622</v>
       </c>
       <c r="C54">
-        <v>19.03314548229842</v>
+        <v>15.45120418201797</v>
       </c>
       <c r="D54">
-        <v>131.1691454822984</v>
+        <v>129.822704182018</v>
       </c>
       <c r="E54">
-        <v>113.796</v>
+        <v>116.0315</v>
       </c>
       <c r="F54">
-        <v>116.246</v>
+        <v>118.4815</v>
       </c>
       <c r="G54">
         <v>4.11</v>
@@ -5715,37 +5715,37 @@
         <v>14.1</v>
       </c>
       <c r="M54">
-        <v>17.0649128</v>
+        <v>17.3930842</v>
       </c>
       <c r="N54">
-        <v>-2.964912800000002</v>
+        <v>-3.293084200000001</v>
       </c>
       <c r="O54">
-        <v>-0.4447369200000003</v>
+        <v>-0.4939626300000001</v>
       </c>
       <c r="P54">
-        <v>-2.520175880000002</v>
+        <v>-2.799121570000001</v>
       </c>
       <c r="Q54">
-        <v>1.179824119999999</v>
+        <v>0.9008784300000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1589756167925611</v>
+        <v>0.1613836086392113</v>
       </c>
       <c r="T54">
-        <v>1.557904965015696</v>
+        <v>1.591051879164966</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1239385178692504</v>
+        <v>0.1216000552679438</v>
       </c>
       <c r="W54">
-        <v>0.1286058255767941</v>
+        <v>0.1289491118866659</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8262567857950026</v>
+        <v>0.8106670351196252</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1441933253603622</v>
+        <v>0.175369714363897</v>
       </c>
       <c r="C55">
-        <v>15.45120418201797</v>
+        <v>-18.02155791228799</v>
       </c>
       <c r="D55">
-        <v>129.822704182018</v>
+        <v>98.58544208771201</v>
       </c>
       <c r="E55">
-        <v>116.0315</v>
+        <v>118.267</v>
       </c>
       <c r="F55">
-        <v>118.4815</v>
+        <v>120.717</v>
       </c>
       <c r="G55">
         <v>4.11</v>
@@ -5797,45 +5797,45 @@
         <v>14.1</v>
       </c>
       <c r="M55">
-        <v>17.3930842</v>
+        <v>24.2399736</v>
       </c>
       <c r="N55">
-        <v>-3.293084200000001</v>
+        <v>-10.1399736</v>
       </c>
       <c r="O55">
-        <v>-0.4939626300000001</v>
+        <v>-1.52099604</v>
       </c>
       <c r="P55">
-        <v>-2.799121570000001</v>
+        <v>-8.618977559999999</v>
       </c>
       <c r="Q55">
-        <v>0.9008784300000001</v>
+        <v>-4.918977559999998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1613836086392113</v>
+        <v>0.1660840979651392</v>
       </c>
       <c r="T55">
-        <v>1.591051879164966</v>
+        <v>1.655755884023968</v>
       </c>
       <c r="U55">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1216000552679438</v>
+        <v>0.08725257027507653</v>
       </c>
       <c r="W55">
-        <v>0.1289491118866659</v>
+        <v>0.1832796838887646</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.8106670351196252</v>
+        <v>0.5816838018338436</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.175369714363897</v>
+        <v>0.176919714363897</v>
       </c>
       <c r="C56">
-        <v>-18.02155791228799</v>
+        <v>-21.42246187901621</v>
       </c>
       <c r="D56">
-        <v>98.58544208771201</v>
+        <v>97.42003812098379</v>
       </c>
       <c r="E56">
-        <v>118.267</v>
+        <v>120.5025</v>
       </c>
       <c r="F56">
-        <v>120.717</v>
+        <v>122.9525</v>
       </c>
       <c r="G56">
         <v>4.11</v>
@@ -5879,37 +5879,37 @@
         <v>14.1</v>
       </c>
       <c r="M56">
-        <v>24.2399736</v>
+        <v>24.688862</v>
       </c>
       <c r="N56">
-        <v>-10.1399736</v>
+        <v>-10.588862</v>
       </c>
       <c r="O56">
-        <v>-1.52099604</v>
+        <v>-1.5883293</v>
       </c>
       <c r="P56">
-        <v>-8.618977559999999</v>
+        <v>-9.000532700000001</v>
       </c>
       <c r="Q56">
-        <v>-4.918977559999998</v>
+        <v>-5.3005327</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1660840979651392</v>
+        <v>0.1687570779199201</v>
       </c>
       <c r="T56">
-        <v>1.655755884023968</v>
+        <v>1.692550459224501</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.08725257027507653</v>
+        <v>0.08566615990643876</v>
       </c>
       <c r="W56">
-        <v>0.1832796838887646</v>
+        <v>0.1835982350907871</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5816838018338436</v>
+        <v>0.5711077327095919</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.176919714363897</v>
+        <v>0.178469714363897</v>
       </c>
       <c r="C57">
-        <v>-21.42246187901621</v>
+        <v>-24.79613467008251</v>
       </c>
       <c r="D57">
-        <v>97.42003812098379</v>
+        <v>96.28186532991749</v>
       </c>
       <c r="E57">
-        <v>120.5025</v>
+        <v>122.738</v>
       </c>
       <c r="F57">
-        <v>122.9525</v>
+        <v>125.188</v>
       </c>
       <c r="G57">
         <v>4.11</v>
@@ -5961,37 +5961,37 @@
         <v>14.1</v>
       </c>
       <c r="M57">
-        <v>24.688862</v>
+        <v>25.1377504</v>
       </c>
       <c r="N57">
-        <v>-10.588862</v>
+        <v>-11.0377504</v>
       </c>
       <c r="O57">
-        <v>-1.5883293</v>
+        <v>-1.65566256</v>
       </c>
       <c r="P57">
-        <v>-9.000532700000001</v>
+        <v>-9.382087840000002</v>
       </c>
       <c r="Q57">
-        <v>-5.3005327</v>
+        <v>-5.682087840000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1687570779199201</v>
+        <v>0.1715515569635547</v>
       </c>
       <c r="T57">
-        <v>1.692550459224501</v>
+        <v>1.731017515115967</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.08566615990643876</v>
+        <v>0.08413640705096664</v>
       </c>
       <c r="W57">
-        <v>0.1835982350907871</v>
+        <v>0.1839054094641659</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5711077327095919</v>
+        <v>0.5609093803397777</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.178469714363897</v>
+        <v>0.180019714363897</v>
       </c>
       <c r="C58">
-        <v>-24.79613467008251</v>
+        <v>-28.1435197010457</v>
       </c>
       <c r="D58">
-        <v>96.28186532991749</v>
+        <v>95.1699802989543</v>
       </c>
       <c r="E58">
-        <v>122.738</v>
+        <v>124.9735</v>
       </c>
       <c r="F58">
-        <v>125.188</v>
+        <v>127.4235</v>
       </c>
       <c r="G58">
         <v>4.11</v>
@@ -6043,37 +6043,37 @@
         <v>14.1</v>
       </c>
       <c r="M58">
-        <v>25.1377504</v>
+        <v>25.5866388</v>
       </c>
       <c r="N58">
-        <v>-11.0377504</v>
+        <v>-11.4866388</v>
       </c>
       <c r="O58">
-        <v>-1.65566256</v>
+        <v>-1.72299582</v>
       </c>
       <c r="P58">
-        <v>-9.382087840000002</v>
+        <v>-9.763642980000004</v>
       </c>
       <c r="Q58">
-        <v>-5.682087840000001</v>
+        <v>-6.063642980000003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1715515569635547</v>
+        <v>0.1744760117766606</v>
       </c>
       <c r="T58">
-        <v>1.731017515115967</v>
+        <v>1.771273736397734</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.08413640705096664</v>
+        <v>0.08266032973428301</v>
       </c>
       <c r="W58">
-        <v>0.1839054094641659</v>
+        <v>0.184201805789356</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5609093803397777</v>
+        <v>0.5510688648952202</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.180019714363897</v>
+        <v>0.181569714363897</v>
       </c>
       <c r="C59">
-        <v>-28.1435197010457</v>
+        <v>-31.46551730586501</v>
       </c>
       <c r="D59">
-        <v>95.1699802989543</v>
+        <v>94.08348269413499</v>
       </c>
       <c r="E59">
-        <v>124.9735</v>
+        <v>127.209</v>
       </c>
       <c r="F59">
-        <v>127.4235</v>
+        <v>129.659</v>
       </c>
       <c r="G59">
         <v>4.11</v>
@@ -6125,37 +6125,37 @@
         <v>14.1</v>
       </c>
       <c r="M59">
-        <v>25.5866388</v>
+        <v>26.0355272</v>
       </c>
       <c r="N59">
-        <v>-11.4866388</v>
+        <v>-11.9355272</v>
       </c>
       <c r="O59">
-        <v>-1.72299582</v>
+        <v>-1.79032908</v>
       </c>
       <c r="P59">
-        <v>-9.763642980000004</v>
+        <v>-10.14519812</v>
       </c>
       <c r="Q59">
-        <v>-6.063642980000003</v>
+        <v>-6.445198120000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1744760117766606</v>
+        <v>0.1775397263427716</v>
       </c>
       <c r="T59">
-        <v>1.771273736397734</v>
+        <v>1.81344692059768</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.08266032973428301</v>
+        <v>0.08123515163541609</v>
       </c>
       <c r="W59">
-        <v>0.184201805789356</v>
+        <v>0.1844879815516084</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5510688648952202</v>
+        <v>0.5415676775694406</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.181569714363897</v>
+        <v>0.183119714363897</v>
       </c>
       <c r="C60">
-        <v>-31.46551730586501</v>
+        <v>-34.76298716832382</v>
       </c>
       <c r="D60">
-        <v>94.08348269413499</v>
+        <v>93.02151283167618</v>
       </c>
       <c r="E60">
-        <v>127.209</v>
+        <v>129.4445</v>
       </c>
       <c r="F60">
-        <v>129.659</v>
+        <v>131.8945</v>
       </c>
       <c r="G60">
         <v>4.11</v>
@@ -6207,37 +6207,37 @@
         <v>14.1</v>
       </c>
       <c r="M60">
-        <v>26.0355272</v>
+        <v>26.4844156</v>
       </c>
       <c r="N60">
-        <v>-11.9355272</v>
+        <v>-12.3844156</v>
       </c>
       <c r="O60">
-        <v>-1.79032908</v>
+        <v>-1.85766234</v>
       </c>
       <c r="P60">
-        <v>-10.14519812</v>
+        <v>-10.52675326</v>
       </c>
       <c r="Q60">
-        <v>-6.445198120000001</v>
+        <v>-6.826753259999998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1775397263427715</v>
+        <v>0.1807528903999123</v>
       </c>
       <c r="T60">
-        <v>1.813446920597679</v>
+        <v>1.857677333295184</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.08123515163541609</v>
+        <v>0.07985828465854464</v>
       </c>
       <c r="W60">
-        <v>0.1844879815516084</v>
+        <v>0.1847644564405642</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5415676775694406</v>
+        <v>0.5323885643902975</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.183119714363897</v>
+        <v>0.184669714363897</v>
       </c>
       <c r="C61">
-        <v>-34.76298716832382</v>
+        <v>-38.03675059062249</v>
       </c>
       <c r="D61">
-        <v>93.02151283167618</v>
+        <v>91.98324940937751</v>
       </c>
       <c r="E61">
-        <v>129.4445</v>
+        <v>131.68</v>
       </c>
       <c r="F61">
-        <v>131.8945</v>
+        <v>134.13</v>
       </c>
       <c r="G61">
         <v>4.11</v>
@@ -6289,37 +6289,37 @@
         <v>14.1</v>
       </c>
       <c r="M61">
-        <v>26.4844156</v>
+        <v>26.933304</v>
       </c>
       <c r="N61">
-        <v>-12.3844156</v>
+        <v>-12.833304</v>
       </c>
       <c r="O61">
-        <v>-1.85766234</v>
+        <v>-1.9249956</v>
       </c>
       <c r="P61">
-        <v>-10.52675326</v>
+        <v>-10.9083084</v>
       </c>
       <c r="Q61">
-        <v>-6.826753259999998</v>
+        <v>-7.208308399999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1807528903999123</v>
+        <v>0.1841267126599102</v>
       </c>
       <c r="T61">
-        <v>1.857677333295184</v>
+        <v>1.904119266627563</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.07985828465854464</v>
+        <v>0.07852731324756887</v>
       </c>
       <c r="W61">
-        <v>0.1847644564405642</v>
+        <v>0.1850317154998882</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5323885643902975</v>
+        <v>0.5235154216504592</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.184669714363897</v>
+        <v>0.1862197143638969</v>
       </c>
       <c r="C62">
-        <v>-38.03675059062249</v>
+        <v>-41.28759261172256</v>
       </c>
       <c r="D62">
-        <v>91.98324940937751</v>
+        <v>90.96790738827744</v>
       </c>
       <c r="E62">
-        <v>131.68</v>
+        <v>133.9155</v>
       </c>
       <c r="F62">
-        <v>134.13</v>
+        <v>136.3655</v>
       </c>
       <c r="G62">
         <v>4.11</v>
@@ -6371,37 +6371,37 @@
         <v>14.1</v>
       </c>
       <c r="M62">
-        <v>26.933304</v>
+        <v>27.3821924</v>
       </c>
       <c r="N62">
-        <v>-12.833304</v>
+        <v>-13.2821924</v>
       </c>
       <c r="O62">
-        <v>-1.9249956</v>
+        <v>-1.99232886</v>
       </c>
       <c r="P62">
-        <v>-10.9083084</v>
+        <v>-11.28986354</v>
       </c>
       <c r="Q62">
-        <v>-7.208308399999998</v>
+        <v>-7.58986354</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1841267126599102</v>
+        <v>0.1876735514460617</v>
       </c>
       <c r="T62">
-        <v>1.904119266627563</v>
+        <v>1.952942837566732</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.07852731324756887</v>
+        <v>0.07723998024351038</v>
       </c>
       <c r="W62">
-        <v>0.1850317154998882</v>
+        <v>0.1852902119671031</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5235154216504592</v>
+        <v>0.5149332016234025</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1862197143638969</v>
+        <v>0.1877697143638969</v>
       </c>
       <c r="C63">
-        <v>-41.28759261172256</v>
+        <v>-44.51626398692459</v>
       </c>
       <c r="D63">
-        <v>90.96790738827744</v>
+        <v>89.97473601307541</v>
       </c>
       <c r="E63">
-        <v>133.9155</v>
+        <v>136.151</v>
       </c>
       <c r="F63">
-        <v>136.3655</v>
+        <v>138.601</v>
       </c>
       <c r="G63">
         <v>4.11</v>
@@ -6453,37 +6453,37 @@
         <v>14.1</v>
       </c>
       <c r="M63">
-        <v>27.3821924</v>
+        <v>27.8310808</v>
       </c>
       <c r="N63">
-        <v>-13.2821924</v>
+        <v>-13.7310808</v>
       </c>
       <c r="O63">
-        <v>-1.99232886</v>
+        <v>-2.05966212</v>
       </c>
       <c r="P63">
-        <v>-11.28986354</v>
+        <v>-11.67141868</v>
       </c>
       <c r="Q63">
-        <v>-7.58986354</v>
+        <v>-7.971418680000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1876735514460617</v>
+        <v>0.1914070659578002</v>
       </c>
       <c r="T63">
-        <v>1.952942837566732</v>
+        <v>2.004336070134277</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.07723998024351038</v>
+        <v>0.07599417411055052</v>
       </c>
       <c r="W63">
-        <v>0.1852902119671031</v>
+        <v>0.1855403698386014</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5149332016234025</v>
+        <v>0.5066278274036702</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1877697143638969</v>
+        <v>0.2117758044826544</v>
       </c>
       <c r="C64">
-        <v>-44.51626398692459</v>
+        <v>-59.76535731080587</v>
       </c>
       <c r="D64">
-        <v>89.97473601307541</v>
+        <v>76.96114268919413</v>
       </c>
       <c r="E64">
-        <v>136.151</v>
+        <v>138.3865</v>
       </c>
       <c r="F64">
-        <v>138.601</v>
+        <v>140.8365</v>
       </c>
       <c r="G64">
         <v>4.11</v>
@@ -6535,45 +6535,45 @@
         <v>14.1</v>
       </c>
       <c r="M64">
-        <v>27.8310808</v>
+        <v>33.2092467</v>
       </c>
       <c r="N64">
-        <v>-13.7310808</v>
+        <v>-19.1092467</v>
       </c>
       <c r="O64">
-        <v>-2.05966212</v>
+        <v>-2.866387005</v>
       </c>
       <c r="P64">
-        <v>-11.67141868</v>
+        <v>-16.242859695</v>
       </c>
       <c r="Q64">
-        <v>-7.971418680000001</v>
+        <v>-12.542859695</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1914070659578002</v>
+        <v>0.1964399329262742</v>
       </c>
       <c r="T64">
-        <v>2.004336070134277</v>
+        <v>2.073615378351527</v>
       </c>
       <c r="U64">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.07599417411055052</v>
+        <v>0.06368708146577741</v>
       </c>
       <c r="W64">
-        <v>0.1855403698386014</v>
+        <v>0.2207825861903697</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.5066278274036702</v>
+        <v>0.4245805431051828</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2117758044826544</v>
+        <v>0.2136758044826544</v>
       </c>
       <c r="C65">
-        <v>-59.76535731080587</v>
+        <v>-62.87189510901686</v>
       </c>
       <c r="D65">
-        <v>76.96114268919413</v>
+        <v>76.09010489098314</v>
       </c>
       <c r="E65">
-        <v>138.3865</v>
+        <v>140.622</v>
       </c>
       <c r="F65">
-        <v>140.8365</v>
+        <v>143.072</v>
       </c>
       <c r="G65">
         <v>4.11</v>
@@ -6617,37 +6617,37 @@
         <v>14.1</v>
       </c>
       <c r="M65">
-        <v>33.2092467</v>
+        <v>33.7363776</v>
       </c>
       <c r="N65">
-        <v>-19.1092467</v>
+        <v>-19.6363776</v>
       </c>
       <c r="O65">
-        <v>-2.866387005</v>
+        <v>-2.94545664</v>
       </c>
       <c r="P65">
-        <v>-16.242859695</v>
+        <v>-16.69092096</v>
       </c>
       <c r="Q65">
-        <v>-12.542859695</v>
+        <v>-12.99092096</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1964399329262742</v>
+        <v>0.2006243755075596</v>
       </c>
       <c r="T65">
-        <v>2.073615378351527</v>
+        <v>2.131215805527959</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06368708146577741</v>
+        <v>0.06269197081787463</v>
       </c>
       <c r="W65">
-        <v>0.2207825861903697</v>
+        <v>0.2210172332811452</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4245805431051828</v>
+        <v>0.4179464721191644</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2136758044826544</v>
+        <v>0.2155758044826543</v>
       </c>
       <c r="C66">
-        <v>-62.87189510901686</v>
+        <v>-65.95893693933485</v>
       </c>
       <c r="D66">
-        <v>76.09010489098314</v>
+        <v>75.23856306066516</v>
       </c>
       <c r="E66">
-        <v>140.622</v>
+        <v>142.8575</v>
       </c>
       <c r="F66">
-        <v>143.072</v>
+        <v>145.3075</v>
       </c>
       <c r="G66">
         <v>4.11</v>
@@ -6699,37 +6699,37 @@
         <v>14.1</v>
       </c>
       <c r="M66">
-        <v>33.7363776</v>
+        <v>34.2635085</v>
       </c>
       <c r="N66">
-        <v>-19.6363776</v>
+        <v>-20.1635085</v>
       </c>
       <c r="O66">
-        <v>-2.94545664</v>
+        <v>-3.024526275</v>
       </c>
       <c r="P66">
-        <v>-16.69092096</v>
+        <v>-17.138982225</v>
       </c>
       <c r="Q66">
-        <v>-12.99092096</v>
+        <v>-13.438982225</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2006243755075596</v>
+        <v>0.2050479290934898</v>
       </c>
       <c r="T66">
-        <v>2.131215805527959</v>
+        <v>2.1921076856859</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06269197081787463</v>
+        <v>0.0617274789591381</v>
       </c>
       <c r="W66">
-        <v>0.2210172332811452</v>
+        <v>0.2212446604614352</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4179464721191644</v>
+        <v>0.4115165263942542</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2155758044826543</v>
+        <v>0.2174758044826544</v>
       </c>
       <c r="C67">
-        <v>-65.95893693933485</v>
+        <v>-69.02713010915019</v>
       </c>
       <c r="D67">
-        <v>75.23856306066516</v>
+        <v>74.40586989084981</v>
       </c>
       <c r="E67">
-        <v>142.8575</v>
+        <v>145.093</v>
       </c>
       <c r="F67">
-        <v>145.3075</v>
+        <v>147.543</v>
       </c>
       <c r="G67">
         <v>4.11</v>
@@ -6781,37 +6781,37 @@
         <v>14.1</v>
       </c>
       <c r="M67">
-        <v>34.2635085</v>
+        <v>34.7906394</v>
       </c>
       <c r="N67">
-        <v>-20.1635085</v>
+        <v>-20.6906394</v>
       </c>
       <c r="O67">
-        <v>-3.024526275</v>
+        <v>-3.10359591</v>
       </c>
       <c r="P67">
-        <v>-17.138982225</v>
+        <v>-17.58704349</v>
       </c>
       <c r="Q67">
-        <v>-13.438982225</v>
+        <v>-13.88704349</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2050479290934898</v>
+        <v>0.2097316917138866</v>
       </c>
       <c r="T67">
-        <v>2.1921076856859</v>
+        <v>2.25658144114725</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0617274789591381</v>
+        <v>0.0607922141264239</v>
       </c>
       <c r="W67">
-        <v>0.2212446604614352</v>
+        <v>0.2214651959089892</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4115165263942542</v>
+        <v>0.4052814275094927</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2174758044826544</v>
+        <v>0.2193758044826544</v>
       </c>
       <c r="C68">
-        <v>-69.02713010915019</v>
+        <v>-72.07709358356115</v>
       </c>
       <c r="D68">
-        <v>74.40586989084981</v>
+        <v>73.59140641643886</v>
       </c>
       <c r="E68">
-        <v>145.093</v>
+        <v>147.3285</v>
       </c>
       <c r="F68">
-        <v>147.543</v>
+        <v>149.7785</v>
       </c>
       <c r="G68">
         <v>4.11</v>
@@ -6863,37 +6863,37 @@
         <v>14.1</v>
       </c>
       <c r="M68">
-        <v>34.7906394</v>
+        <v>35.31777030000001</v>
       </c>
       <c r="N68">
-        <v>-20.6906394</v>
+        <v>-21.21777030000001</v>
       </c>
       <c r="O68">
-        <v>-3.10359591</v>
+        <v>-3.182665545000001</v>
       </c>
       <c r="P68">
-        <v>-17.58704349</v>
+        <v>-18.03510475500001</v>
       </c>
       <c r="Q68">
-        <v>-13.88704349</v>
+        <v>-14.33510475500001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2097316917138866</v>
+        <v>0.2146993187355195</v>
       </c>
       <c r="T68">
-        <v>2.25658144114725</v>
+        <v>2.324962696939591</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0607922141264239</v>
+        <v>0.05988486764692502</v>
       </c>
       <c r="W68">
-        <v>0.2214651959089892</v>
+        <v>0.2216791482088551</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4052814275094927</v>
+        <v>0.3992324509795002</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2193758044826544</v>
+        <v>0.2212758044826544</v>
       </c>
       <c r="C69">
-        <v>-72.07709358356115</v>
+        <v>-75.10941951978334</v>
       </c>
       <c r="D69">
-        <v>73.59140641643886</v>
+        <v>72.79458048021667</v>
       </c>
       <c r="E69">
-        <v>147.3285</v>
+        <v>149.564</v>
       </c>
       <c r="F69">
-        <v>149.7785</v>
+        <v>152.014</v>
       </c>
       <c r="G69">
         <v>4.11</v>
@@ -6945,37 +6945,37 @@
         <v>14.1</v>
       </c>
       <c r="M69">
-        <v>35.31777030000001</v>
+        <v>35.8449012</v>
       </c>
       <c r="N69">
-        <v>-21.21777030000001</v>
+        <v>-21.7449012</v>
       </c>
       <c r="O69">
-        <v>-3.182665545000001</v>
+        <v>-3.26173518</v>
       </c>
       <c r="P69">
-        <v>-18.03510475500001</v>
+        <v>-18.48316602</v>
       </c>
       <c r="Q69">
-        <v>-14.33510475500001</v>
+        <v>-14.78316602</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2146993187355195</v>
+        <v>0.2199774224460045</v>
       </c>
       <c r="T69">
-        <v>2.324962696939591</v>
+        <v>2.397617781218953</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05988486764692502</v>
+        <v>0.0590042078285879</v>
       </c>
       <c r="W69">
-        <v>0.2216791482088551</v>
+        <v>0.221886807794019</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3992324509795002</v>
+        <v>0.3933613855239194</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2212758044826544</v>
+        <v>0.2231758044826544</v>
       </c>
       <c r="C70">
-        <v>-75.10941951978334</v>
+        <v>-78.12467470294271</v>
       </c>
       <c r="D70">
-        <v>72.79458048021667</v>
+        <v>72.0148252970573</v>
       </c>
       <c r="E70">
-        <v>149.564</v>
+        <v>151.7995</v>
       </c>
       <c r="F70">
-        <v>152.014</v>
+        <v>154.2495</v>
       </c>
       <c r="G70">
         <v>4.11</v>
@@ -7027,37 +7027,37 @@
         <v>14.1</v>
       </c>
       <c r="M70">
-        <v>35.8449012</v>
+        <v>36.37203210000001</v>
       </c>
       <c r="N70">
-        <v>-21.7449012</v>
+        <v>-22.2720321</v>
       </c>
       <c r="O70">
-        <v>-3.26173518</v>
+        <v>-3.340804815000001</v>
       </c>
       <c r="P70">
-        <v>-18.48316602</v>
+        <v>-18.931227285</v>
       </c>
       <c r="Q70">
-        <v>-14.78316602</v>
+        <v>-15.231227285</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2199774224460045</v>
+        <v>0.2255960489765208</v>
       </c>
       <c r="T70">
-        <v>2.397617781218953</v>
+        <v>2.474960290290533</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0590042078285879</v>
+        <v>0.05814907438179676</v>
       </c>
       <c r="W70">
-        <v>0.221886807794019</v>
+        <v>0.2220884482607723</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3933613855239194</v>
+        <v>0.3876604958786452</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2231758044826544</v>
+        <v>0.2250758044826544</v>
       </c>
       <c r="C71">
-        <v>-78.12467470294271</v>
+        <v>-81.12340189056718</v>
       </c>
       <c r="D71">
-        <v>72.0148252970573</v>
+        <v>71.25159810943283</v>
       </c>
       <c r="E71">
-        <v>151.7995</v>
+        <v>154.035</v>
       </c>
       <c r="F71">
-        <v>154.2495</v>
+        <v>156.485</v>
       </c>
       <c r="G71">
         <v>4.11</v>
@@ -7109,37 +7109,37 @@
         <v>14.1</v>
       </c>
       <c r="M71">
-        <v>36.37203210000001</v>
+        <v>36.899163</v>
       </c>
       <c r="N71">
-        <v>-22.2720321</v>
+        <v>-22.799163</v>
       </c>
       <c r="O71">
-        <v>-3.340804815000001</v>
+        <v>-3.41987445</v>
       </c>
       <c r="P71">
-        <v>-18.931227285</v>
+        <v>-19.37928855</v>
       </c>
       <c r="Q71">
-        <v>-15.231227285</v>
+        <v>-15.67928855</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2255960489765208</v>
+        <v>0.2315892506090715</v>
       </c>
       <c r="T71">
-        <v>2.474960290290533</v>
+        <v>2.557458966633551</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05814907438179676</v>
+        <v>0.05731837331919967</v>
       </c>
       <c r="W71">
-        <v>0.2220884482607723</v>
+        <v>0.2222843275713327</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3876604958786452</v>
+        <v>0.3821224887946646</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2250758044826544</v>
+        <v>0.2269758044826544</v>
       </c>
       <c r="C72">
-        <v>-81.12340189056718</v>
+        <v>-84.10612107247999</v>
       </c>
       <c r="D72">
-        <v>71.25159810943283</v>
+        <v>70.50437892752002</v>
       </c>
       <c r="E72">
-        <v>154.035</v>
+        <v>156.2705</v>
       </c>
       <c r="F72">
-        <v>156.485</v>
+        <v>158.7205</v>
       </c>
       <c r="G72">
         <v>4.11</v>
@@ -7191,37 +7191,37 @@
         <v>14.1</v>
       </c>
       <c r="M72">
-        <v>36.899163</v>
+        <v>37.4262939</v>
       </c>
       <c r="N72">
-        <v>-22.799163</v>
+        <v>-23.3262939</v>
       </c>
       <c r="O72">
-        <v>-3.41987445</v>
+        <v>-3.498944085</v>
       </c>
       <c r="P72">
-        <v>-19.37928855</v>
+        <v>-19.827349815</v>
       </c>
       <c r="Q72">
-        <v>-15.67928855</v>
+        <v>-16.127349815</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2315892506090715</v>
+        <v>0.237995776492143</v>
       </c>
       <c r="T72">
-        <v>2.557458966633551</v>
+        <v>2.645647206862294</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05731837331919967</v>
+        <v>0.05651107228653488</v>
       </c>
       <c r="W72">
-        <v>0.2222843275713327</v>
+        <v>0.2224746891548351</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3821224887946646</v>
+        <v>0.3767404819102326</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2269758044826544</v>
+        <v>0.2288758044826543</v>
       </c>
       <c r="C73">
-        <v>-84.10612107247994</v>
+        <v>-87.07333065224026</v>
       </c>
       <c r="D73">
-        <v>70.50437892752005</v>
+        <v>69.77266934775973</v>
       </c>
       <c r="E73">
-        <v>156.2705</v>
+        <v>158.506</v>
       </c>
       <c r="F73">
-        <v>158.7205</v>
+        <v>160.956</v>
       </c>
       <c r="G73">
         <v>4.11</v>
@@ -7273,37 +7273,37 @@
         <v>14.1</v>
       </c>
       <c r="M73">
-        <v>37.4262939</v>
+        <v>37.9534248</v>
       </c>
       <c r="N73">
-        <v>-23.3262939</v>
+        <v>-23.8534248</v>
       </c>
       <c r="O73">
-        <v>-3.498944084999999</v>
+        <v>-3.57801372</v>
       </c>
       <c r="P73">
-        <v>-19.827349815</v>
+        <v>-20.27541108</v>
       </c>
       <c r="Q73">
-        <v>-16.127349815</v>
+        <v>-16.57541107999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2379957764921429</v>
+        <v>0.2448599113668623</v>
       </c>
       <c r="T73">
-        <v>2.645647206862293</v>
+        <v>2.740134607107375</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05651107228653489</v>
+        <v>0.05572619628255524</v>
       </c>
       <c r="W73">
-        <v>0.2224746891548351</v>
+        <v>0.2226597629165735</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3767404819102327</v>
+        <v>0.371507975217035</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2288758044826543</v>
+        <v>0.2307758044826543</v>
       </c>
       <c r="C74">
-        <v>-87.07333065224026</v>
+        <v>-90.02550855577211</v>
       </c>
       <c r="D74">
-        <v>69.77266934775973</v>
+        <v>69.05599144422789</v>
       </c>
       <c r="E74">
-        <v>158.506</v>
+        <v>160.7415</v>
       </c>
       <c r="F74">
-        <v>160.956</v>
+        <v>163.1915</v>
       </c>
       <c r="G74">
         <v>4.11</v>
@@ -7355,37 +7355,37 @@
         <v>14.1</v>
       </c>
       <c r="M74">
-        <v>37.9534248</v>
+        <v>38.4805557</v>
       </c>
       <c r="N74">
-        <v>-23.8534248</v>
+        <v>-24.3805557</v>
       </c>
       <c r="O74">
-        <v>-3.57801372</v>
+        <v>-3.657083354999999</v>
       </c>
       <c r="P74">
-        <v>-20.27541108</v>
+        <v>-20.723472345</v>
       </c>
       <c r="Q74">
-        <v>-16.57541107999999</v>
+        <v>-17.02347234499999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2448599113668623</v>
+        <v>0.2522325006767461</v>
       </c>
       <c r="T74">
-        <v>2.740134607107375</v>
+        <v>2.841621074037278</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05572619628255524</v>
+        <v>0.05496282373073942</v>
       </c>
       <c r="W74">
-        <v>0.2226597629165735</v>
+        <v>0.2228397661642916</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.371507975217035</v>
+        <v>0.3664188248715962</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2307758044826543</v>
+        <v>0.2326758044826543</v>
       </c>
       <c r="C75">
-        <v>-90.02550855577211</v>
+        <v>-92.96311327236323</v>
       </c>
       <c r="D75">
-        <v>69.05599144422789</v>
+        <v>68.35388672763676</v>
       </c>
       <c r="E75">
-        <v>160.7415</v>
+        <v>162.977</v>
       </c>
       <c r="F75">
-        <v>163.1915</v>
+        <v>165.427</v>
       </c>
       <c r="G75">
         <v>4.11</v>
@@ -7437,37 +7437,37 @@
         <v>14.1</v>
       </c>
       <c r="M75">
-        <v>38.4805557</v>
+        <v>39.0076866</v>
       </c>
       <c r="N75">
-        <v>-24.3805557</v>
+        <v>-24.9076866</v>
       </c>
       <c r="O75">
-        <v>-3.657083354999999</v>
+        <v>-3.736152989999999</v>
       </c>
       <c r="P75">
-        <v>-20.723472345</v>
+        <v>-21.17153361</v>
       </c>
       <c r="Q75">
-        <v>-17.02347234499999</v>
+        <v>-17.47153360999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2522325006767461</v>
+        <v>0.2601722122412363</v>
       </c>
       <c r="T75">
-        <v>2.841621074037278</v>
+        <v>2.95091419226948</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05496282373073942</v>
+        <v>0.05422008286951321</v>
       </c>
       <c r="W75">
-        <v>0.2228397661642916</v>
+        <v>0.2230149044593688</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3664188248715962</v>
+        <v>0.3614672191300881</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2326758044826543</v>
+        <v>0.2345758044826544</v>
       </c>
       <c r="C76">
-        <v>-92.96311327236323</v>
+        <v>-95.88658483279933</v>
       </c>
       <c r="D76">
-        <v>68.35388672763676</v>
+        <v>67.66591516720067</v>
       </c>
       <c r="E76">
-        <v>162.977</v>
+        <v>165.2125</v>
       </c>
       <c r="F76">
-        <v>165.427</v>
+        <v>167.6625</v>
       </c>
       <c r="G76">
         <v>4.11</v>
@@ -7519,37 +7519,37 @@
         <v>14.1</v>
       </c>
       <c r="M76">
-        <v>39.0076866</v>
+        <v>39.5348175</v>
       </c>
       <c r="N76">
-        <v>-24.9076866</v>
+        <v>-25.4348175</v>
       </c>
       <c r="O76">
-        <v>-3.736152989999999</v>
+        <v>-3.815222625</v>
       </c>
       <c r="P76">
-        <v>-21.17153361</v>
+        <v>-21.619594875</v>
       </c>
       <c r="Q76">
-        <v>-17.47153360999999</v>
+        <v>-17.919594875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2601722122412363</v>
+        <v>0.2687471007308858</v>
       </c>
       <c r="T76">
-        <v>2.95091419226948</v>
+        <v>3.06895075996026</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05422008286951321</v>
+        <v>0.05349714843125303</v>
       </c>
       <c r="W76">
-        <v>0.2230149044593688</v>
+        <v>0.2231853723999106</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3614672191300881</v>
+        <v>0.3566476562083536</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2345758044826544</v>
+        <v>0.2364758044826543</v>
       </c>
       <c r="C77">
-        <v>-95.88658483279933</v>
+        <v>-98.79634572901796</v>
       </c>
       <c r="D77">
-        <v>67.66591516720067</v>
+        <v>66.99165427098204</v>
       </c>
       <c r="E77">
-        <v>165.2125</v>
+        <v>167.448</v>
       </c>
       <c r="F77">
-        <v>167.6625</v>
+        <v>169.898</v>
       </c>
       <c r="G77">
         <v>4.11</v>
@@ -7601,37 +7601,37 @@
         <v>14.1</v>
       </c>
       <c r="M77">
-        <v>39.5348175</v>
+        <v>40.0619484</v>
       </c>
       <c r="N77">
-        <v>-25.4348175</v>
+        <v>-25.9619484</v>
       </c>
       <c r="O77">
-        <v>-3.815222625</v>
+        <v>-3.894292259999999</v>
       </c>
       <c r="P77">
-        <v>-21.619594875</v>
+        <v>-22.06765614</v>
       </c>
       <c r="Q77">
-        <v>-17.919594875</v>
+        <v>-18.36765613999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2687471007308858</v>
+        <v>0.2780365632613394</v>
       </c>
       <c r="T77">
-        <v>3.06895075996026</v>
+        <v>3.196823708291938</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05349714843125303</v>
+        <v>0.05279323858347339</v>
       </c>
       <c r="W77">
-        <v>0.2231853723999106</v>
+        <v>0.223351354342017</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3566476562083536</v>
+        <v>0.3519549238898226</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2364758044826543</v>
+        <v>0.2383758044826543</v>
       </c>
       <c r="C78">
-        <v>-98.79634572901796</v>
+        <v>-101.6928017793214</v>
       </c>
       <c r="D78">
-        <v>66.99165427098204</v>
+        <v>66.33069822067858</v>
       </c>
       <c r="E78">
-        <v>167.448</v>
+        <v>169.6835</v>
       </c>
       <c r="F78">
-        <v>169.898</v>
+        <v>172.1335</v>
       </c>
       <c r="G78">
         <v>4.11</v>
@@ -7683,37 +7683,37 @@
         <v>14.1</v>
       </c>
       <c r="M78">
-        <v>40.0619484</v>
+        <v>40.5890793</v>
       </c>
       <c r="N78">
-        <v>-25.9619484</v>
+        <v>-26.4890793</v>
       </c>
       <c r="O78">
-        <v>-3.894292259999999</v>
+        <v>-3.973361895</v>
       </c>
       <c r="P78">
-        <v>-22.06765614</v>
+        <v>-22.515717405</v>
       </c>
       <c r="Q78">
-        <v>-18.36765613999999</v>
+        <v>-18.815717405</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2780365632613394</v>
+        <v>0.2881338051422672</v>
       </c>
       <c r="T78">
-        <v>3.196823708291938</v>
+        <v>3.335816043435065</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05279323858347339</v>
+        <v>0.05210761210836334</v>
       </c>
       <c r="W78">
-        <v>0.223351354342017</v>
+        <v>0.2235130250648479</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3519549238898226</v>
+        <v>0.3473840807224223</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2383758044826543</v>
+        <v>0.2402758044826544</v>
       </c>
       <c r="C79">
-        <v>-101.6928017793214</v>
+        <v>-104.5763429428716</v>
       </c>
       <c r="D79">
-        <v>66.33069822067858</v>
+        <v>65.68265705712844</v>
       </c>
       <c r="E79">
-        <v>169.6835</v>
+        <v>171.919</v>
       </c>
       <c r="F79">
-        <v>172.1335</v>
+        <v>174.369</v>
       </c>
       <c r="G79">
         <v>4.11</v>
@@ -7765,37 +7765,37 @@
         <v>14.1</v>
       </c>
       <c r="M79">
-        <v>40.5890793</v>
+        <v>41.1162102</v>
       </c>
       <c r="N79">
-        <v>-26.4890793</v>
+        <v>-27.0162102</v>
       </c>
       <c r="O79">
-        <v>-3.973361895</v>
+        <v>-4.052431530000001</v>
       </c>
       <c r="P79">
-        <v>-22.515717405</v>
+        <v>-22.96377867</v>
       </c>
       <c r="Q79">
-        <v>-18.815717405</v>
+        <v>-19.26377867</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2881338051422672</v>
+        <v>0.2991489781032793</v>
       </c>
       <c r="T79">
-        <v>3.335816043435065</v>
+        <v>3.487444045409386</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05210761210836334</v>
+        <v>0.05143956579928176</v>
       </c>
       <c r="W79">
-        <v>0.2235130250648479</v>
+        <v>0.2236705503845294</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3473840807224223</v>
+        <v>0.3429304386618784</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2402758044826544</v>
+        <v>0.2421758044826544</v>
       </c>
       <c r="C80">
-        <v>-104.5763429428716</v>
+        <v>-107.4473440869016</v>
       </c>
       <c r="D80">
-        <v>65.68265705712844</v>
+        <v>65.04715591309841</v>
       </c>
       <c r="E80">
-        <v>171.919</v>
+        <v>174.1545</v>
       </c>
       <c r="F80">
-        <v>174.369</v>
+        <v>176.6045</v>
       </c>
       <c r="G80">
         <v>4.11</v>
@@ -7847,37 +7847,37 @@
         <v>14.1</v>
       </c>
       <c r="M80">
-        <v>41.1162102</v>
+        <v>41.6433411</v>
       </c>
       <c r="N80">
-        <v>-27.0162102</v>
+        <v>-27.5433411</v>
       </c>
       <c r="O80">
-        <v>-4.052431530000001</v>
+        <v>-4.131501165</v>
       </c>
       <c r="P80">
-        <v>-22.96377867</v>
+        <v>-23.411839935</v>
       </c>
       <c r="Q80">
-        <v>-19.26377867</v>
+        <v>-19.711839935</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2991489781032793</v>
+        <v>0.3112132151558165</v>
       </c>
       <c r="T80">
-        <v>3.487444045409386</v>
+        <v>3.653512809476501</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05143956579928176</v>
+        <v>0.05078843205498706</v>
       </c>
       <c r="W80">
-        <v>0.2236705503845294</v>
+        <v>0.2238240877214341</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3429304386618784</v>
+        <v>0.3385895470332471</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2421758044826544</v>
+        <v>0.2440758044826543</v>
       </c>
       <c r="C81">
-        <v>-107.4473440869016</v>
+        <v>-110.3061657098165</v>
       </c>
       <c r="D81">
-        <v>65.04715591309841</v>
+        <v>64.42383429018351</v>
       </c>
       <c r="E81">
-        <v>174.1545</v>
+        <v>176.39</v>
       </c>
       <c r="F81">
-        <v>176.6045</v>
+        <v>178.84</v>
       </c>
       <c r="G81">
         <v>4.11</v>
@@ -7929,37 +7929,37 @@
         <v>14.1</v>
       </c>
       <c r="M81">
-        <v>41.6433411</v>
+        <v>42.170472</v>
       </c>
       <c r="N81">
-        <v>-27.5433411</v>
+        <v>-28.070472</v>
       </c>
       <c r="O81">
-        <v>-4.131501165</v>
+        <v>-4.2105708</v>
       </c>
       <c r="P81">
-        <v>-23.411839935</v>
+        <v>-23.8599012</v>
       </c>
       <c r="Q81">
-        <v>-19.711839935</v>
+        <v>-20.1599012</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3112132151558165</v>
+        <v>0.3244838759136073</v>
       </c>
       <c r="T81">
-        <v>3.653512809476501</v>
+        <v>3.836188449950325</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05078843205498706</v>
+        <v>0.05015357665429971</v>
       </c>
       <c r="W81">
-        <v>0.2238240877214341</v>
+        <v>0.2239737866249161</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3385895470332471</v>
+        <v>0.3343571776953315</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2440758044826543</v>
+        <v>0.2459758044826543</v>
       </c>
       <c r="C82">
-        <v>-110.3061657098165</v>
+        <v>-113.153154623113</v>
       </c>
       <c r="D82">
-        <v>64.42383429018351</v>
+        <v>63.81234537688703</v>
       </c>
       <c r="E82">
-        <v>176.39</v>
+        <v>178.6255</v>
       </c>
       <c r="F82">
-        <v>178.84</v>
+        <v>181.0755</v>
       </c>
       <c r="G82">
         <v>4.11</v>
@@ -8011,37 +8011,37 @@
         <v>14.1</v>
       </c>
       <c r="M82">
-        <v>42.170472</v>
+        <v>42.6976029</v>
       </c>
       <c r="N82">
-        <v>-28.070472</v>
+        <v>-28.5976029</v>
       </c>
       <c r="O82">
-        <v>-4.2105708</v>
+        <v>-4.289640435</v>
       </c>
       <c r="P82">
-        <v>-23.8599012</v>
+        <v>-24.307962465</v>
       </c>
       <c r="Q82">
-        <v>-20.1599012</v>
+        <v>-20.607962465</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3244838759136073</v>
+        <v>0.3391514483301129</v>
       </c>
       <c r="T82">
-        <v>3.836188449950325</v>
+        <v>4.038093105210869</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05015357665429971</v>
+        <v>0.04953439669560466</v>
       </c>
       <c r="W82">
-        <v>0.2239737866249161</v>
+        <v>0.2241197892591764</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3343571776953315</v>
+        <v>0.3302293113040311</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2459758044826543</v>
+        <v>0.2478758044826544</v>
       </c>
       <c r="C83">
-        <v>-113.153154623113</v>
+        <v>-115.9886445948292</v>
       </c>
       <c r="D83">
-        <v>63.81234537688703</v>
+        <v>63.21235540517078</v>
       </c>
       <c r="E83">
-        <v>178.6255</v>
+        <v>180.861</v>
       </c>
       <c r="F83">
-        <v>181.0755</v>
+        <v>183.311</v>
       </c>
       <c r="G83">
         <v>4.11</v>
@@ -8093,37 +8093,37 @@
         <v>14.1</v>
       </c>
       <c r="M83">
-        <v>42.6976029</v>
+        <v>43.2247338</v>
       </c>
       <c r="N83">
-        <v>-28.5976029</v>
+        <v>-29.1247338</v>
       </c>
       <c r="O83">
-        <v>-4.289640435</v>
+        <v>-4.36871007</v>
       </c>
       <c r="P83">
-        <v>-24.307962465</v>
+        <v>-24.75602373</v>
       </c>
       <c r="Q83">
-        <v>-20.607962465</v>
+        <v>-21.05602373</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3391514483301129</v>
+        <v>0.3554487510151192</v>
       </c>
       <c r="T83">
-        <v>4.038093105210869</v>
+        <v>4.262431611055918</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04953439669560466</v>
+        <v>0.04893031868712167</v>
       </c>
       <c r="W83">
-        <v>0.2241197892591764</v>
+        <v>0.2242622308535767</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3302293113040311</v>
+        <v>0.3262021245808112</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2478758044826544</v>
+        <v>0.2497758044826544</v>
       </c>
       <c r="C84">
-        <v>-115.9886445948292</v>
+        <v>-118.8129569570329</v>
       </c>
       <c r="D84">
-        <v>63.21235540517078</v>
+        <v>62.62354304296711</v>
       </c>
       <c r="E84">
-        <v>180.861</v>
+        <v>183.0965</v>
       </c>
       <c r="F84">
-        <v>183.311</v>
+        <v>185.5465</v>
       </c>
       <c r="G84">
         <v>4.11</v>
@@ -8175,37 +8175,37 @@
         <v>14.1</v>
       </c>
       <c r="M84">
-        <v>43.2247338</v>
+        <v>43.75186470000001</v>
       </c>
       <c r="N84">
-        <v>-29.1247338</v>
+        <v>-29.6518647</v>
       </c>
       <c r="O84">
-        <v>-4.36871007</v>
+        <v>-4.447779705</v>
       </c>
       <c r="P84">
-        <v>-24.75602373</v>
+        <v>-25.204084995</v>
       </c>
       <c r="Q84">
-        <v>-21.05602373</v>
+        <v>-21.504084995</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3554487510151192</v>
+        <v>0.3736633834277733</v>
       </c>
       <c r="T84">
-        <v>4.262431611055918</v>
+        <v>4.513162882294502</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04893031868712167</v>
+        <v>0.04834079677522863</v>
       </c>
       <c r="W84">
-        <v>0.2242622308535767</v>
+        <v>0.2244012401204011</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3262021245808112</v>
+        <v>0.3222719785015243</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2497758044826544</v>
+        <v>0.2516758044826544</v>
       </c>
       <c r="C85">
-        <v>-118.8129569570329</v>
+        <v>-121.6264011796706</v>
       </c>
       <c r="D85">
-        <v>62.62354304296711</v>
+        <v>62.04559882032938</v>
       </c>
       <c r="E85">
-        <v>183.0965</v>
+        <v>185.332</v>
       </c>
       <c r="F85">
-        <v>185.5465</v>
+        <v>187.782</v>
       </c>
       <c r="G85">
         <v>4.11</v>
@@ -8257,37 +8257,37 @@
         <v>14.1</v>
       </c>
       <c r="M85">
-        <v>43.75186470000001</v>
+        <v>44.2789956</v>
       </c>
       <c r="N85">
-        <v>-29.6518647</v>
+        <v>-30.1789956</v>
       </c>
       <c r="O85">
-        <v>-4.447779705</v>
+        <v>-4.52684934</v>
       </c>
       <c r="P85">
-        <v>-25.204084995</v>
+        <v>-25.65214626</v>
       </c>
       <c r="Q85">
-        <v>-21.504084995</v>
+        <v>-21.95214626</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3736633834277733</v>
+        <v>0.3941548448920092</v>
       </c>
       <c r="T85">
-        <v>4.513162882294502</v>
+        <v>4.795235562437909</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04834079677522863</v>
+        <v>0.04776531109933306</v>
       </c>
       <c r="W85">
-        <v>0.2244012401204011</v>
+        <v>0.2245369396427773</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3222719785015243</v>
+        <v>0.3184354073288871</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2516758044826544</v>
+        <v>0.2535758044826543</v>
       </c>
       <c r="C86">
-        <v>-121.6264011796706</v>
+        <v>-124.429275412932</v>
       </c>
       <c r="D86">
-        <v>62.04559882032941</v>
+        <v>61.47822458706798</v>
       </c>
       <c r="E86">
-        <v>185.332</v>
+        <v>187.5675</v>
       </c>
       <c r="F86">
-        <v>187.782</v>
+        <v>190.0175</v>
       </c>
       <c r="G86">
         <v>4.11</v>
@@ -8339,37 +8339,37 @@
         <v>14.1</v>
       </c>
       <c r="M86">
-        <v>44.27899559999999</v>
+        <v>44.8061265</v>
       </c>
       <c r="N86">
-        <v>-30.17899559999999</v>
+        <v>-30.7061265</v>
       </c>
       <c r="O86">
-        <v>-4.526849339999999</v>
+        <v>-4.605918974999999</v>
       </c>
       <c r="P86">
-        <v>-25.65214625999999</v>
+        <v>-26.100207525</v>
       </c>
       <c r="Q86">
-        <v>-21.95214625999999</v>
+        <v>-22.400207525</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.394154844892009</v>
+        <v>0.4173785012181429</v>
       </c>
       <c r="T86">
-        <v>4.795235562437906</v>
+        <v>5.114917933267099</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04776531109933307</v>
+        <v>0.04720336626287033</v>
       </c>
       <c r="W86">
-        <v>0.2245369396427773</v>
+        <v>0.2246694462352152</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3184354073288872</v>
+        <v>0.3146891084191356</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2535758044826543</v>
+        <v>0.2554758044826543</v>
       </c>
       <c r="C87">
-        <v>-124.429275412932</v>
+        <v>-127.221867000126</v>
       </c>
       <c r="D87">
-        <v>61.47822458706798</v>
+        <v>60.92113299987395</v>
       </c>
       <c r="E87">
-        <v>187.5675</v>
+        <v>189.803</v>
       </c>
       <c r="F87">
-        <v>190.0175</v>
+        <v>192.253</v>
       </c>
       <c r="G87">
         <v>4.11</v>
@@ -8421,37 +8421,37 @@
         <v>14.1</v>
       </c>
       <c r="M87">
-        <v>44.8061265</v>
+        <v>45.3332574</v>
       </c>
       <c r="N87">
-        <v>-30.7061265</v>
+        <v>-31.2332574</v>
       </c>
       <c r="O87">
-        <v>-4.605918974999999</v>
+        <v>-4.68498861</v>
       </c>
       <c r="P87">
-        <v>-26.100207525</v>
+        <v>-26.54826879</v>
       </c>
       <c r="Q87">
-        <v>-22.400207525</v>
+        <v>-22.84826879</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4173785012181429</v>
+        <v>0.4439198227337246</v>
       </c>
       <c r="T87">
-        <v>5.114917933267099</v>
+        <v>5.48026921421475</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04720336626287033</v>
+        <v>0.04665448991097648</v>
       </c>
       <c r="W87">
-        <v>0.2246694462352152</v>
+        <v>0.2247988712789918</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3146891084191356</v>
+        <v>0.3110299327398433</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2554758044826543</v>
+        <v>0.2573758044826543</v>
       </c>
       <c r="C88">
-        <v>-127.221867000126</v>
+        <v>-130.0044529629222</v>
       </c>
       <c r="D88">
-        <v>60.92113299987395</v>
+        <v>60.37404703707779</v>
       </c>
       <c r="E88">
-        <v>189.803</v>
+        <v>192.0385</v>
       </c>
       <c r="F88">
-        <v>192.253</v>
+        <v>194.4885</v>
       </c>
       <c r="G88">
         <v>4.11</v>
@@ -8503,37 +8503,37 @@
         <v>14.1</v>
       </c>
       <c r="M88">
-        <v>45.3332574</v>
+        <v>45.8603883</v>
       </c>
       <c r="N88">
-        <v>-31.2332574</v>
+        <v>-31.7603883</v>
       </c>
       <c r="O88">
-        <v>-4.68498861</v>
+        <v>-4.764058244999999</v>
       </c>
       <c r="P88">
-        <v>-26.54826879</v>
+        <v>-26.99633005499999</v>
       </c>
       <c r="Q88">
-        <v>-22.84826879</v>
+        <v>-23.29633005499999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4439198227337246</v>
+        <v>0.4745444244824726</v>
       </c>
       <c r="T88">
-        <v>5.48026921421475</v>
+        <v>5.901828384538961</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04665448991097648</v>
+        <v>0.04611823140625262</v>
       </c>
       <c r="W88">
-        <v>0.2247988712789918</v>
+        <v>0.2249253210344057</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3110299327398433</v>
+        <v>0.3074548760416842</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2573758044826543</v>
+        <v>0.2592758044826544</v>
       </c>
       <c r="C89">
-        <v>-130.0044529629222</v>
+        <v>-132.7773004606793</v>
       </c>
       <c r="D89">
-        <v>60.37404703707779</v>
+        <v>59.83669953932066</v>
       </c>
       <c r="E89">
-        <v>192.0385</v>
+        <v>194.274</v>
       </c>
       <c r="F89">
-        <v>194.4885</v>
+        <v>196.724</v>
       </c>
       <c r="G89">
         <v>4.11</v>
@@ -8585,37 +8585,37 @@
         <v>14.1</v>
       </c>
       <c r="M89">
-        <v>45.8603883</v>
+        <v>46.3875192</v>
       </c>
       <c r="N89">
-        <v>-31.7603883</v>
+        <v>-32.2875192</v>
       </c>
       <c r="O89">
-        <v>-4.764058244999999</v>
+        <v>-4.84312788</v>
       </c>
       <c r="P89">
-        <v>-26.99633005499999</v>
+        <v>-27.44439132</v>
       </c>
       <c r="Q89">
-        <v>-23.29633005499999</v>
+        <v>-23.74439132</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4745444244824726</v>
+        <v>0.5102731265226788</v>
       </c>
       <c r="T89">
-        <v>5.901828384538961</v>
+        <v>6.393647416583875</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04611823140625262</v>
+        <v>0.04559416059481793</v>
       </c>
       <c r="W89">
-        <v>0.2249253210344057</v>
+        <v>0.2250488969317419</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3074548760416842</v>
+        <v>0.3039610706321195</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2592758044826544</v>
+        <v>0.2611758044826544</v>
       </c>
       <c r="C90">
-        <v>-132.7773004606793</v>
+        <v>-135.540667225462</v>
       </c>
       <c r="D90">
-        <v>59.83669953932066</v>
+        <v>59.30883277453803</v>
       </c>
       <c r="E90">
-        <v>194.274</v>
+        <v>196.5095</v>
       </c>
       <c r="F90">
-        <v>196.724</v>
+        <v>198.9595</v>
       </c>
       <c r="G90">
         <v>4.11</v>
@@ -8667,37 +8667,37 @@
         <v>14.1</v>
       </c>
       <c r="M90">
-        <v>46.3875192</v>
+        <v>46.9146501</v>
       </c>
       <c r="N90">
-        <v>-32.2875192</v>
+        <v>-32.8146501</v>
       </c>
       <c r="O90">
-        <v>-4.84312788</v>
+        <v>-4.922197515</v>
       </c>
       <c r="P90">
-        <v>-27.44439132</v>
+        <v>-27.892452585</v>
       </c>
       <c r="Q90">
-        <v>-23.74439132</v>
+        <v>-24.192452585</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5102731265226788</v>
+        <v>0.5524979562065585</v>
       </c>
       <c r="T90">
-        <v>6.393647416583875</v>
+        <v>6.974888090818773</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04559416059481793</v>
+        <v>0.0450818666555503</v>
       </c>
       <c r="W90">
-        <v>0.2250488969317419</v>
+        <v>0.2251696958426213</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3039610706321195</v>
+        <v>0.3005457777036687</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2611758044826544</v>
+        <v>0.2630758044826543</v>
       </c>
       <c r="C91">
-        <v>-135.540667225462</v>
+        <v>-138.2948019742318</v>
       </c>
       <c r="D91">
-        <v>59.30883277453803</v>
+        <v>58.79019802576823</v>
       </c>
       <c r="E91">
-        <v>196.5095</v>
+        <v>198.745</v>
       </c>
       <c r="F91">
-        <v>198.9595</v>
+        <v>201.195</v>
       </c>
       <c r="G91">
         <v>4.11</v>
@@ -8749,37 +8749,37 @@
         <v>14.1</v>
       </c>
       <c r="M91">
-        <v>46.9146501</v>
+        <v>47.441781</v>
       </c>
       <c r="N91">
-        <v>-32.8146501</v>
+        <v>-33.341781</v>
       </c>
       <c r="O91">
-        <v>-4.922197515</v>
+        <v>-5.001267149999999</v>
       </c>
       <c r="P91">
-        <v>-27.892452585</v>
+        <v>-28.34051385</v>
       </c>
       <c r="Q91">
-        <v>-24.192452585</v>
+        <v>-24.64051385</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5524979562065585</v>
+        <v>0.6031677518272145</v>
       </c>
       <c r="T91">
-        <v>6.974888090818773</v>
+        <v>7.672376899900651</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0450818666555503</v>
+        <v>0.0445809570260442</v>
       </c>
       <c r="W91">
-        <v>0.2251696958426213</v>
+        <v>0.2252878103332588</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3005457777036687</v>
+        <v>0.297206380173628</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2630758044826543</v>
+        <v>0.2649758044826543</v>
       </c>
       <c r="C92">
-        <v>-138.2948019742318</v>
+        <v>-141.0399447996003</v>
       </c>
       <c r="D92">
-        <v>58.79019802576823</v>
+        <v>58.28055520039969</v>
       </c>
       <c r="E92">
-        <v>198.745</v>
+        <v>200.9805</v>
       </c>
       <c r="F92">
-        <v>201.195</v>
+        <v>203.4305</v>
       </c>
       <c r="G92">
         <v>4.11</v>
@@ -8831,37 +8831,37 @@
         <v>14.1</v>
       </c>
       <c r="M92">
-        <v>47.441781</v>
+        <v>47.9689119</v>
       </c>
       <c r="N92">
-        <v>-33.341781</v>
+        <v>-33.8689119</v>
       </c>
       <c r="O92">
-        <v>-5.001267149999999</v>
+        <v>-5.080336785</v>
       </c>
       <c r="P92">
-        <v>-28.34051385</v>
+        <v>-28.788575115</v>
       </c>
       <c r="Q92">
-        <v>-24.64051385</v>
+        <v>-25.088575115</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6031677518272145</v>
+        <v>0.6650975020302384</v>
       </c>
       <c r="T92">
-        <v>7.672376899900651</v>
+        <v>8.524863222111836</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0445809570260442</v>
+        <v>0.04409105639938437</v>
       </c>
       <c r="W92">
-        <v>0.2252878103332588</v>
+        <v>0.2254033289010252</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.297206380173628</v>
+        <v>0.2939403759958958</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2649758044826543</v>
+        <v>0.2668758044826544</v>
       </c>
       <c r="C93">
-        <v>-141.0399447996003</v>
+        <v>-143.7763275404316</v>
       </c>
       <c r="D93">
-        <v>58.28055520039969</v>
+        <v>57.77967245956837</v>
       </c>
       <c r="E93">
-        <v>200.9805</v>
+        <v>203.216</v>
       </c>
       <c r="F93">
-        <v>203.4305</v>
+        <v>205.666</v>
       </c>
       <c r="G93">
         <v>4.11</v>
@@ -8913,37 +8913,37 @@
         <v>14.1</v>
       </c>
       <c r="M93">
-        <v>47.9689119</v>
+        <v>48.4960428</v>
       </c>
       <c r="N93">
-        <v>-33.8689119</v>
+        <v>-34.3960428</v>
       </c>
       <c r="O93">
-        <v>-5.080336785</v>
+        <v>-5.159406419999999</v>
       </c>
       <c r="P93">
-        <v>-28.788575115</v>
+        <v>-29.23663638</v>
       </c>
       <c r="Q93">
-        <v>-25.088575115</v>
+        <v>-25.53663638</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6650975020302384</v>
+        <v>0.7425096897840183</v>
       </c>
       <c r="T93">
-        <v>8.524863222111836</v>
+        <v>9.590471124875817</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04409105639938437</v>
+        <v>0.04361180578634758</v>
       </c>
       <c r="W93">
-        <v>0.2254033289010252</v>
+        <v>0.2255163361955792</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2939403759958958</v>
+        <v>0.290745371908984</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2668758044826544</v>
+        <v>0.2687758044826544</v>
       </c>
       <c r="C94">
-        <v>-143.7763275404316</v>
+        <v>-146.5041741334976</v>
       </c>
       <c r="D94">
-        <v>57.77967245956837</v>
+        <v>57.28732586650241</v>
       </c>
       <c r="E94">
-        <v>203.216</v>
+        <v>205.4515</v>
       </c>
       <c r="F94">
-        <v>205.666</v>
+        <v>207.9015</v>
       </c>
       <c r="G94">
         <v>4.11</v>
@@ -8995,37 +8995,37 @@
         <v>14.1</v>
       </c>
       <c r="M94">
-        <v>48.4960428</v>
+        <v>49.0231737</v>
       </c>
       <c r="N94">
-        <v>-34.3960428</v>
+        <v>-34.9231737</v>
       </c>
       <c r="O94">
-        <v>-5.159406419999999</v>
+        <v>-5.238476055</v>
       </c>
       <c r="P94">
-        <v>-29.23663638</v>
+        <v>-29.684697645</v>
       </c>
       <c r="Q94">
-        <v>-25.53663638</v>
+        <v>-25.984697645</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7425096897840183</v>
+        <v>0.8420396454674496</v>
       </c>
       <c r="T94">
-        <v>9.590471124875817</v>
+        <v>10.96053842842951</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04361180578634758</v>
+        <v>0.04314286163810728</v>
       </c>
       <c r="W94">
-        <v>0.2255163361955792</v>
+        <v>0.2256269132257343</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.290745371908984</v>
+        <v>0.2876190775873819</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2687758044826544</v>
+        <v>0.2706758044826544</v>
       </c>
       <c r="C95">
-        <v>-146.5041741334976</v>
+        <v>-149.2237009473061</v>
       </c>
       <c r="D95">
-        <v>57.28732586650241</v>
+        <v>56.80329905269394</v>
       </c>
       <c r="E95">
-        <v>205.4515</v>
+        <v>207.687</v>
       </c>
       <c r="F95">
-        <v>207.9015</v>
+        <v>210.137</v>
       </c>
       <c r="G95">
         <v>4.11</v>
@@ -9077,37 +9077,37 @@
         <v>14.1</v>
       </c>
       <c r="M95">
-        <v>49.0231737</v>
+        <v>49.5503046</v>
       </c>
       <c r="N95">
-        <v>-34.9231737</v>
+        <v>-35.4503046</v>
       </c>
       <c r="O95">
-        <v>-5.238476055</v>
+        <v>-5.31754569</v>
       </c>
       <c r="P95">
-        <v>-29.684697645</v>
+        <v>-30.13275891</v>
       </c>
       <c r="Q95">
-        <v>-25.984697645</v>
+        <v>-26.43275891</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8420396454674496</v>
+        <v>0.9747462530453582</v>
       </c>
       <c r="T95">
-        <v>10.96053842842951</v>
+        <v>12.78729483316776</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04314286163810728</v>
+        <v>0.04268389502493593</v>
       </c>
       <c r="W95">
-        <v>0.2256269132257343</v>
+        <v>0.2257351375531201</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2876190775873819</v>
+        <v>0.2845593001662395</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2706758044826544</v>
+        <v>0.2725758044826543</v>
       </c>
       <c r="C96">
-        <v>-149.2237009473061</v>
+        <v>-151.9351170991474</v>
       </c>
       <c r="D96">
-        <v>56.80329905269394</v>
+        <v>56.32738290085256</v>
       </c>
       <c r="E96">
-        <v>207.687</v>
+        <v>209.9225</v>
       </c>
       <c r="F96">
-        <v>210.137</v>
+        <v>212.3725</v>
       </c>
       <c r="G96">
         <v>4.11</v>
@@ -9159,37 +9159,37 @@
         <v>14.1</v>
       </c>
       <c r="M96">
-        <v>49.5503046</v>
+        <v>50.0774355</v>
       </c>
       <c r="N96">
-        <v>-35.4503046</v>
+        <v>-35.9774355</v>
       </c>
       <c r="O96">
-        <v>-5.31754569</v>
+        <v>-5.396615325</v>
       </c>
       <c r="P96">
-        <v>-30.13275891</v>
+        <v>-30.580820175</v>
       </c>
       <c r="Q96">
-        <v>-26.43275891</v>
+        <v>-26.880820175</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9747462530453582</v>
+        <v>1.16053550365443</v>
       </c>
       <c r="T96">
-        <v>12.78729483316776</v>
+        <v>15.34475379980132</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04268389502493593</v>
+        <v>0.04223459086677871</v>
       </c>
       <c r="W96">
-        <v>0.2257351375531201</v>
+        <v>0.2258410834736136</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2845593001662395</v>
+        <v>0.2815639391118581</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2725758044826543</v>
+        <v>0.2744758044826544</v>
       </c>
       <c r="C97">
-        <v>-151.9351170991474</v>
+        <v>-154.6386247563359</v>
       </c>
       <c r="D97">
-        <v>56.32738290085256</v>
+        <v>55.85937524366407</v>
       </c>
       <c r="E97">
-        <v>209.9225</v>
+        <v>212.158</v>
       </c>
       <c r="F97">
-        <v>212.3725</v>
+        <v>214.608</v>
       </c>
       <c r="G97">
         <v>4.11</v>
@@ -9241,37 +9241,37 @@
         <v>14.1</v>
       </c>
       <c r="M97">
-        <v>50.0774355</v>
+        <v>50.6045664</v>
       </c>
       <c r="N97">
-        <v>-35.9774355</v>
+        <v>-36.5045664</v>
       </c>
       <c r="O97">
-        <v>-5.396615325</v>
+        <v>-5.47568496</v>
       </c>
       <c r="P97">
-        <v>-30.580820175</v>
+        <v>-31.02888144</v>
       </c>
       <c r="Q97">
-        <v>-26.880820175</v>
+        <v>-27.32888144</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.16053550365443</v>
+        <v>1.439219379568039</v>
       </c>
       <c r="T97">
-        <v>15.34475379980132</v>
+        <v>19.18094224975166</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04223459086677871</v>
+        <v>0.04179464721191643</v>
       </c>
       <c r="W97">
-        <v>0.2258410834736136</v>
+        <v>0.2259448221874301</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2815639391118581</v>
+        <v>0.2786309814127762</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2744758044826544</v>
+        <v>0.2763758044826544</v>
       </c>
       <c r="C98">
-        <v>-154.6386247563359</v>
+        <v>-157.3344194225568</v>
       </c>
       <c r="D98">
-        <v>55.85937524366407</v>
+        <v>55.39908057744316</v>
       </c>
       <c r="E98">
-        <v>212.158</v>
+        <v>214.3935</v>
       </c>
       <c r="F98">
-        <v>214.608</v>
+        <v>216.8435</v>
       </c>
       <c r="G98">
         <v>4.11</v>
@@ -9323,37 +9323,37 @@
         <v>14.1</v>
       </c>
       <c r="M98">
-        <v>50.6045664</v>
+        <v>51.1316973</v>
       </c>
       <c r="N98">
-        <v>-36.50456639999999</v>
+        <v>-37.0316973</v>
       </c>
       <c r="O98">
-        <v>-5.475684959999999</v>
+        <v>-5.554754594999999</v>
       </c>
       <c r="P98">
-        <v>-31.02888144</v>
+        <v>-31.476942705</v>
       </c>
       <c r="Q98">
-        <v>-27.32888144</v>
+        <v>-27.776942705</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.439219379568035</v>
+        <v>1.903692506090713</v>
       </c>
       <c r="T98">
-        <v>19.18094224975161</v>
+        <v>25.57458966633548</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04179464721191644</v>
+        <v>0.04136377456024719</v>
       </c>
       <c r="W98">
-        <v>0.2259448221874301</v>
+        <v>0.2260464219586937</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2786309814127763</v>
+        <v>0.2757584970683147</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2763758044826544</v>
+        <v>0.2782758044826544</v>
       </c>
       <c r="C99">
-        <v>-157.3344194225568</v>
+        <v>-160.0226902101722</v>
       </c>
       <c r="D99">
-        <v>55.39908057744316</v>
+        <v>54.94630978982772</v>
       </c>
       <c r="E99">
-        <v>214.3935</v>
+        <v>216.629</v>
       </c>
       <c r="F99">
-        <v>216.8435</v>
+        <v>219.079</v>
       </c>
       <c r="G99">
         <v>4.11</v>
@@ -9405,37 +9405,37 @@
         <v>14.1</v>
       </c>
       <c r="M99">
-        <v>51.1316973</v>
+        <v>51.65882819999999</v>
       </c>
       <c r="N99">
-        <v>-37.0316973</v>
+        <v>-37.55882819999999</v>
       </c>
       <c r="O99">
-        <v>-5.554754594999999</v>
+        <v>-5.633824229999999</v>
       </c>
       <c r="P99">
-        <v>-31.476942705</v>
+        <v>-31.92500397</v>
       </c>
       <c r="Q99">
-        <v>-27.776942705</v>
+        <v>-28.22500397</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.903692506090713</v>
+        <v>2.83263875913607</v>
       </c>
       <c r="T99">
-        <v>25.57458966633548</v>
+        <v>38.36188449950322</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04136377456024719</v>
+        <v>0.04094169522799977</v>
       </c>
       <c r="W99">
-        <v>0.2260464219586937</v>
+        <v>0.2261459482652377</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2757584970683147</v>
+        <v>0.2729446348533319</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2782758044826544</v>
+        <v>0.2801758044826543</v>
       </c>
       <c r="C100">
-        <v>-160.0226902101722</v>
+        <v>-162.7036200992818</v>
       </c>
       <c r="D100">
-        <v>54.94630978982772</v>
+        <v>54.50087990071816</v>
       </c>
       <c r="E100">
-        <v>216.629</v>
+        <v>218.8645</v>
       </c>
       <c r="F100">
-        <v>219.079</v>
+        <v>221.3145</v>
       </c>
       <c r="G100">
         <v>4.11</v>
@@ -9487,37 +9487,37 @@
         <v>14.1</v>
       </c>
       <c r="M100">
-        <v>51.65882819999999</v>
+        <v>52.1859591</v>
       </c>
       <c r="N100">
-        <v>-37.55882819999999</v>
+        <v>-38.0859591</v>
       </c>
       <c r="O100">
-        <v>-5.633824229999999</v>
+        <v>-5.712893864999999</v>
       </c>
       <c r="P100">
-        <v>-31.92500397</v>
+        <v>-32.373065235</v>
       </c>
       <c r="Q100">
-        <v>-28.22500397</v>
+        <v>-28.673065235</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.83263875913607</v>
+        <v>5.61947751827214</v>
       </c>
       <c r="T100">
-        <v>38.36188449950322</v>
+        <v>76.72376899900644</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04094169522799977</v>
+        <v>0.04052814275094927</v>
       </c>
       <c r="W100">
-        <v>0.2261459482652377</v>
+        <v>0.2262434639393262</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2729446348533319</v>
+        <v>0.2701876183396619</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2801758044826543</v>
-      </c>
-      <c r="C101">
-        <v>-162.7036200992818</v>
-      </c>
-      <c r="D101">
-        <v>54.50087990071816</v>
-      </c>
-      <c r="E101">
-        <v>218.8645</v>
-      </c>
-      <c r="F101">
-        <v>221.3145</v>
-      </c>
-      <c r="G101">
-        <v>4.11</v>
-      </c>
-      <c r="H101">
-        <v>221.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>17.8</v>
-      </c>
-      <c r="K101">
-        <v>3.700000000000001</v>
-      </c>
-      <c r="L101">
-        <v>14.1</v>
-      </c>
-      <c r="M101">
-        <v>52.1859591</v>
-      </c>
-      <c r="N101">
-        <v>-38.0859591</v>
-      </c>
-      <c r="O101">
-        <v>-5.712893864999999</v>
-      </c>
-      <c r="P101">
-        <v>-32.373065235</v>
-      </c>
-      <c r="Q101">
-        <v>-28.673065235</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.61947751827214</v>
-      </c>
-      <c r="T101">
-        <v>76.72376899900644</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04052814275094927</v>
-      </c>
-      <c r="W101">
-        <v>0.2262434639393262</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2701876183396619</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
